--- a/Sabana Datos/params_2k1b_all_families.xlsx
+++ b/Sabana Datos/params_2k1b_all_families.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="14" uniqueCount="14">
   <si>
     <t>subject_id</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>h_2k1b_diff_k</t>
+  </si>
+  <si>
+    <t>grupo</t>
   </si>
 </sst>
 </file>
@@ -97,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="true"/>
@@ -113,6 +116,7 @@
     <col min="11" max="11" width="14.42578125" customWidth="true"/>
     <col min="12" max="12" width="14.42578125" customWidth="true"/>
     <col min="13" max="13" width="15.85546875" customWidth="true"/>
+    <col min="14" max="14" width="6.28515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -155,6 +159,9 @@
       <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
@@ -196,6 +203,9 @@
       <c r="M2" s="0">
         <v>1.6568225949972437</v>
       </c>
+      <c r="N2" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
@@ -237,6 +247,9 @@
       <c r="M3" s="0">
         <v>0.98774357378681787</v>
       </c>
+      <c r="N3" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
@@ -278,6 +291,9 @@
       <c r="M4" s="0">
         <v>213.88451639084107</v>
       </c>
+      <c r="N4" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
@@ -319,6 +335,9 @@
       <c r="M5" s="0">
         <v>583.3408679557192</v>
       </c>
+      <c r="N5" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
@@ -360,6 +379,9 @@
       <c r="M6" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N6" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -401,6 +423,9 @@
       <c r="M7" s="0">
         <v>0.91122622413031906</v>
       </c>
+      <c r="N7" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
@@ -442,6 +467,9 @@
       <c r="M8" s="0">
         <v>9434072923105.2305</v>
       </c>
+      <c r="N8" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
@@ -483,6 +511,9 @@
       <c r="M9" s="0">
         <v>0.003609265241170001</v>
       </c>
+      <c r="N9" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
@@ -524,6 +555,9 @@
       <c r="M10" s="0">
         <v>1.9374207216815471</v>
       </c>
+      <c r="N10" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
@@ -565,6 +599,9 @@
       <c r="M11" s="0">
         <v>0.80942122156116247</v>
       </c>
+      <c r="N11" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
@@ -606,6 +643,9 @@
       <c r="M12" s="0">
         <v>0.024896330788109197</v>
       </c>
+      <c r="N12" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
@@ -647,6 +687,9 @@
       <c r="M13" s="0">
         <v>12.467797215908128</v>
       </c>
+      <c r="N13" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
@@ -688,6 +731,9 @@
       <c r="M14" s="0">
         <v>1.2234850927933509</v>
       </c>
+      <c r="N14" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
@@ -729,6 +775,9 @@
       <c r="M15" s="0">
         <v>15141850787759.621</v>
       </c>
+      <c r="N15" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
@@ -770,6 +819,9 @@
       <c r="M16" s="0">
         <v>2.4085163163463661</v>
       </c>
+      <c r="N16" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
@@ -811,6 +863,9 @@
       <c r="M17" s="0">
         <v>1.248133052945873</v>
       </c>
+      <c r="N17" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
@@ -852,6 +907,9 @@
       <c r="M18" s="0">
         <v>0.85608984945952293</v>
       </c>
+      <c r="N18" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
@@ -893,6 +951,9 @@
       <c r="M19" s="0">
         <v>3.3352016218955982</v>
       </c>
+      <c r="N19" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
@@ -934,6 +995,9 @@
       <c r="M20" s="0">
         <v>1.522102759613722</v>
       </c>
+      <c r="N20" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
@@ -975,6 +1039,9 @@
       <c r="M21" s="0">
         <v>-0.55052538297960196</v>
       </c>
+      <c r="N21" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
@@ -1016,6 +1083,9 @@
       <c r="M22" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N22" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
@@ -1057,6 +1127,9 @@
       <c r="M23" s="0">
         <v>-0.58103026950290793</v>
       </c>
+      <c r="N23" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
@@ -1098,6 +1171,9 @@
       <c r="M24" s="0">
         <v>0.73839225890995208</v>
       </c>
+      <c r="N24" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
@@ -1139,6 +1215,9 @@
       <c r="M25" s="0">
         <v>1.91456981786207</v>
       </c>
+      <c r="N25" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
@@ -1180,6 +1259,9 @@
       <c r="M26" s="0">
         <v>2.8129399851258139</v>
       </c>
+      <c r="N26" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
@@ -1221,6 +1303,9 @@
       <c r="M27" s="0">
         <v>0.81668766573334506</v>
       </c>
+      <c r="N27" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
@@ -1262,6 +1347,9 @@
       <c r="M28" s="0">
         <v>0.96845043446748602</v>
       </c>
+      <c r="N28" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
@@ -1303,6 +1391,9 @@
       <c r="M29" s="0">
         <v>1.7485005592478919</v>
       </c>
+      <c r="N29" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
@@ -1344,6 +1435,9 @@
       <c r="M30" s="0">
         <v>701.61961885092819</v>
       </c>
+      <c r="N30" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
@@ -1385,6 +1479,9 @@
       <c r="M31" s="0">
         <v>3.2600332255748241</v>
       </c>
+      <c r="N31" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
@@ -1426,6 +1523,9 @@
       <c r="M32" s="0">
         <v>0.7080055812336401</v>
       </c>
+      <c r="N32" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
@@ -1467,6 +1567,9 @@
       <c r="M33" s="0">
         <v>1.8587860708139901</v>
       </c>
+      <c r="N33" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
@@ -1508,6 +1611,9 @@
       <c r="M34" s="0">
         <v>-0.090730506596647997</v>
       </c>
+      <c r="N34" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
@@ -1549,6 +1655,9 @@
       <c r="M35" s="0">
         <v>-0.28534289528136297</v>
       </c>
+      <c r="N35" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
@@ -1590,6 +1699,9 @@
       <c r="M36" s="0">
         <v>3.0050764429488752</v>
       </c>
+      <c r="N36" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
@@ -1631,6 +1743,9 @@
       <c r="M37" s="0">
         <v>0.27994862953067101</v>
       </c>
+      <c r="N37" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
@@ -1672,6 +1787,9 @@
       <c r="M38" s="0">
         <v>213.88451639084107</v>
       </c>
+      <c r="N38" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
@@ -1713,6 +1831,9 @@
       <c r="M39" s="0">
         <v>0.5930295545193065</v>
       </c>
+      <c r="N39" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
@@ -1754,6 +1875,9 @@
       <c r="M40" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N40" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
@@ -1795,6 +1919,9 @@
       <c r="M41" s="0">
         <v>62.487436803758705</v>
       </c>
+      <c r="N41" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
@@ -1836,6 +1963,9 @@
       <c r="M42" s="0">
         <v>1.5815253032782675</v>
       </c>
+      <c r="N42" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
@@ -1877,6 +2007,9 @@
       <c r="M43" s="0">
         <v>1.7581540392408963</v>
       </c>
+      <c r="N43" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
@@ -1918,6 +2051,9 @@
       <c r="M44" s="0">
         <v>-0.51049693643764193</v>
       </c>
+      <c r="N44" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -1959,6 +2095,9 @@
       <c r="M45" s="0">
         <v>1.812996349330052</v>
       </c>
+      <c r="N45" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
@@ -2000,6 +2139,9 @@
       <c r="M46" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N46" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
@@ -2041,6 +2183,9 @@
       <c r="M47" s="0">
         <v>683.60950407001792</v>
       </c>
+      <c r="N47" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
@@ -2082,6 +2227,9 @@
       <c r="M48" s="0">
         <v>6.0950968427772807</v>
       </c>
+      <c r="N48" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
@@ -2123,6 +2271,9 @@
       <c r="M49" s="0">
         <v>0.67389464190483228</v>
       </c>
+      <c r="N49" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
@@ -2164,6 +2315,9 @@
       <c r="M50" s="0">
         <v>278.98057547298362</v>
       </c>
+      <c r="N50" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
@@ -2205,6 +2359,9 @@
       <c r="M51" s="0">
         <v>11.44603503758491</v>
       </c>
+      <c r="N51" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
@@ -2246,6 +2403,9 @@
       <c r="M52" s="0">
         <v>1.4951930765858061</v>
       </c>
+      <c r="N52" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
@@ -2287,6 +2447,9 @@
       <c r="M53" s="0">
         <v>211.98535123698252</v>
       </c>
+      <c r="N53" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
@@ -2328,6 +2491,9 @@
       <c r="M54" s="0">
         <v>0.087053506284563195</v>
       </c>
+      <c r="N54" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
@@ -2369,6 +2535,9 @@
       <c r="M55" s="0">
         <v>213.88451639084107</v>
       </c>
+      <c r="N55" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
@@ -2410,6 +2579,9 @@
       <c r="M56" s="0">
         <v>-2.8365939225352008</v>
       </c>
+      <c r="N56" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
@@ -2451,6 +2623,9 @@
       <c r="M57" s="0">
         <v>0.83930625170496653</v>
       </c>
+      <c r="N57" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
@@ -2492,6 +2667,9 @@
       <c r="M58" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N58" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
@@ -2533,6 +2711,9 @@
       <c r="M59" s="0">
         <v>-0.012577596234092402</v>
       </c>
+      <c r="N59" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
@@ -2574,6 +2755,9 @@
       <c r="M60" s="0">
         <v>291.54955529718029</v>
       </c>
+      <c r="N60" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
@@ -2615,6 +2799,9 @@
       <c r="M61" s="0">
         <v>233.34502851395092</v>
       </c>
+      <c r="N61" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
@@ -2656,6 +2843,9 @@
       <c r="M62" s="0">
         <v>2.5485994964672614</v>
       </c>
+      <c r="N62" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
@@ -2697,6 +2887,9 @@
       <c r="M63" s="0">
         <v>3.191857318646552</v>
       </c>
+      <c r="N63" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
@@ -2738,6 +2931,9 @@
       <c r="M64" s="0">
         <v>194.81037997486885</v>
       </c>
+      <c r="N64" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
@@ -2779,6 +2975,9 @@
       <c r="M65" s="0">
         <v>3.5911072814187301</v>
       </c>
+      <c r="N65" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
@@ -2820,6 +3019,9 @@
       <c r="M66" s="0">
         <v>0.17821349506012302</v>
       </c>
+      <c r="N66" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
@@ -2861,6 +3063,9 @@
       <c r="M67" s="0">
         <v>0.14714491829954129</v>
       </c>
+      <c r="N67" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
@@ -2902,6 +3107,9 @@
       <c r="M68" s="0">
         <v>320.73824114666115</v>
       </c>
+      <c r="N68" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
@@ -2943,6 +3151,9 @@
       <c r="M69" s="0">
         <v>253.96633136250188</v>
       </c>
+      <c r="N69" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
@@ -2984,6 +3195,9 @@
       <c r="M70" s="0">
         <v>2.5680844722451779</v>
       </c>
+      <c r="N70" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
@@ -3025,6 +3239,9 @@
       <c r="M71" s="0">
         <v>1.010793297278443</v>
       </c>
+      <c r="N71" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
@@ -3066,6 +3283,9 @@
       <c r="M72" s="0">
         <v>1.7213070874787773</v>
       </c>
+      <c r="N72" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
@@ -3107,6 +3327,9 @@
       <c r="M73" s="0">
         <v>243.96006487941935</v>
       </c>
+      <c r="N73" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
@@ -3148,6 +3371,9 @@
       <c r="M74" s="0">
         <v>3.7273054684411058</v>
       </c>
+      <c r="N74" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
@@ -3189,6 +3415,9 @@
       <c r="M75" s="0">
         <v>0.96095402630945093</v>
       </c>
+      <c r="N75" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
@@ -3230,6 +3459,9 @@
       <c r="M76" s="0">
         <v>0.8245186770513917</v>
       </c>
+      <c r="N76" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
@@ -3271,6 +3503,9 @@
       <c r="M77" s="0">
         <v>12.402491077370883</v>
       </c>
+      <c r="N77" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
@@ -3312,6 +3547,9 @@
       <c r="M78" s="0">
         <v>7.400268257782777</v>
       </c>
+      <c r="N78" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
@@ -3353,6 +3591,9 @@
       <c r="M79" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N79" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
@@ -3394,6 +3635,9 @@
       <c r="M80" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N80" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
@@ -3435,6 +3679,9 @@
       <c r="M81" s="0">
         <v>256.13339674074501</v>
       </c>
+      <c r="N81" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
@@ -3476,6 +3723,9 @@
       <c r="M82" s="0">
         <v>265.82915539316548</v>
       </c>
+      <c r="N82" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -3517,6 +3767,9 @@
       <c r="M83" s="0">
         <v>1.0493688867284781</v>
       </c>
+      <c r="N83" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
@@ -3558,6 +3811,9 @@
       <c r="M84" s="0">
         <v>1.9942139889718804</v>
       </c>
+      <c r="N84" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
@@ -3599,6 +3855,9 @@
       <c r="M85" s="0">
         <v>0.95022379227391596</v>
       </c>
+      <c r="N85" s="0">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>

--- a/Sabana Datos/params_2k1b_all_families.xlsx
+++ b/Sabana Datos/params_2k1b_all_families.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="14">
   <si>
     <t>subject_id</t>
   </si>
@@ -103,20 +103,20 @@
   <dimension ref="A1:N85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" customWidth="true"/>
-    <col min="3" max="3" width="15.28515625" customWidth="true"/>
-    <col min="4" max="4" width="15.5703125" customWidth="true"/>
-    <col min="5" max="5" width="15.7109375" customWidth="true"/>
-    <col min="6" max="6" width="14.7109375" customWidth="true"/>
-    <col min="7" max="7" width="14.42578125" customWidth="true"/>
-    <col min="8" max="8" width="16.42578125" customWidth="true"/>
-    <col min="9" max="9" width="16.5703125" customWidth="true"/>
-    <col min="10" max="10" width="13.42578125" customWidth="true"/>
-    <col min="11" max="11" width="14.42578125" customWidth="true"/>
-    <col min="12" max="12" width="14.42578125" customWidth="true"/>
-    <col min="13" max="13" width="15.85546875" customWidth="true"/>
-    <col min="14" max="14" width="6.28515625" customWidth="true"/>
+    <col min="1" max="1" width="9.21875" customWidth="true"/>
+    <col min="2" max="2" width="15.5546875" customWidth="true"/>
+    <col min="3" max="3" width="14.21875" customWidth="true"/>
+    <col min="4" max="4" width="15.21875" customWidth="true"/>
+    <col min="5" max="5" width="15.5546875" customWidth="true"/>
+    <col min="6" max="6" width="13.6640625" customWidth="true"/>
+    <col min="7" max="7" width="15.21875" customWidth="true"/>
+    <col min="8" max="8" width="15.5546875" customWidth="true"/>
+    <col min="9" max="9" width="14.21875" customWidth="true"/>
+    <col min="10" max="10" width="15.21875" customWidth="true"/>
+    <col min="11" max="11" width="14.21875" customWidth="true"/>
+    <col min="12" max="12" width="14.5546875" customWidth="true"/>
+    <col min="13" max="13" width="14.21875" customWidth="true"/>
+    <col min="14" max="14" width="5.6640625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -168,40 +168,40 @@
         <v>155</v>
       </c>
       <c r="B2" s="0">
-        <v>1.48505528664597e-08</v>
+        <v>1.4924234696747601e-08</v>
       </c>
       <c r="C2" s="0">
-        <v>0.255226181372608</v>
+        <v>0.72679724470339901</v>
       </c>
       <c r="D2" s="0">
-        <v>1.8195209122154099</v>
+        <v>1.8195218945812499</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.22398290135840301</v>
+        <v>1.7585353415989299e-09</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.60863352569138096</v>
+        <v>0.68108742212788898</v>
       </c>
       <c r="G2" s="0">
-        <v>1.5642320639112901</v>
+        <v>1.8195215683008901</v>
       </c>
       <c r="H2" s="0">
-        <v>0.000428883872673744</v>
+        <v>0.00043261228452632901</v>
       </c>
       <c r="I2" s="0">
-        <v>-1.6563937111245699</v>
+        <v>0.70996095901203005</v>
       </c>
       <c r="J2" s="0">
-        <v>1.82120830548208</v>
+        <v>1.8212503392181301</v>
       </c>
       <c r="K2" s="0">
-        <v>-0.25522616652205515</v>
+        <v>-0.72679722977916428</v>
       </c>
       <c r="L2" s="0">
-        <v>0.38465062433297792</v>
+        <v>-0.68108742036935366</v>
       </c>
       <c r="M2" s="0">
-        <v>1.6568225949972437</v>
+        <v>-0.70952834672750376</v>
       </c>
       <c r="N2" s="0">
         <v>0</v>
@@ -212,40 +212,40 @@
         <v>332</v>
       </c>
       <c r="B3" s="0">
-        <v>1.6205557685464799e-07</v>
+        <v>1.5152813341831901e-07</v>
       </c>
       <c r="C3" s="0">
-        <v>0.25121017929086498</v>
+        <v>0.71706542918278604</v>
       </c>
       <c r="D3" s="0">
-        <v>1.51360680906905</v>
+        <v>1.5136059283347301</v>
       </c>
       <c r="E3" s="0">
-        <v>-0.0265307059383793</v>
+        <v>6.3861588319930598e-08</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.90330449812448299</v>
+        <v>0.73177620812885902</v>
       </c>
       <c r="G3" s="0">
-        <v>1.48253691070549</v>
+        <v>1.51360569502095</v>
       </c>
       <c r="H3" s="0">
-        <v>0.0158069019430499</v>
+        <v>0.015805371668726399</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.97193667184376797</v>
+        <v>0.69011335083041003</v>
       </c>
       <c r="J3" s="0">
-        <v>1.55879688413024</v>
+        <v>1.5588273867053599</v>
       </c>
       <c r="K3" s="0">
-        <v>-0.25121001723528813</v>
+        <v>-0.71706527765465267</v>
       </c>
       <c r="L3" s="0">
-        <v>0.87677379218610374</v>
+        <v>-0.73177614426727067</v>
       </c>
       <c r="M3" s="0">
-        <v>0.98774357378681787</v>
+        <v>-0.67430797916168361</v>
       </c>
       <c r="N3" s="0">
         <v>1</v>
@@ -256,40 +256,40 @@
         <v>548</v>
       </c>
       <c r="B4" s="0">
-        <v>2.6580093912461199e-09</v>
+        <v>1.4393815425029799e-08</v>
       </c>
       <c r="C4" s="0">
-        <v>0.25005232893581197</v>
+        <v>0.75005326865598798</v>
       </c>
       <c r="D4" s="0">
-        <v>20.402800524072799</v>
+        <v>18.837836752021602</v>
       </c>
       <c r="E4" s="0">
-        <v>-24.965</v>
+        <v>4.53176926514867e-08</v>
       </c>
       <c r="F4" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.72452799175771798</v>
       </c>
       <c r="G4" s="0">
-        <v>37.108333333333299</v>
+        <v>18.5805086084296</v>
       </c>
       <c r="H4" s="0">
-        <v>-0.24455113207891399</v>
+        <v>4.4701824257886297e-08</v>
       </c>
       <c r="I4" s="0">
-        <v>-214.12906752292</v>
+        <v>0.75000003996341602</v>
       </c>
       <c r="J4" s="0">
-        <v>121.357744015259</v>
+        <v>18.837092869611102</v>
       </c>
       <c r="K4" s="0">
-        <v>-0.25005232627780261</v>
+        <v>-0.75005325426217251</v>
       </c>
       <c r="L4" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.72452794644002538</v>
       </c>
       <c r="M4" s="0">
-        <v>213.88451639084107</v>
+        <v>-0.74999999526159178</v>
       </c>
       <c r="N4" s="0">
         <v>0</v>
@@ -300,40 +300,40 @@
         <v>849</v>
       </c>
       <c r="B5" s="0">
-        <v>1.76662183126797e-10</v>
+        <v>5.4146245636362297e-11</v>
       </c>
       <c r="C5" s="0">
-        <v>0.39710585122168901</v>
+        <v>0.54218260242185601</v>
       </c>
       <c r="D5" s="0">
-        <v>15.0618464242551</v>
+        <v>49.852019880382798</v>
       </c>
       <c r="E5" s="0">
-        <v>-24.965</v>
+        <v>4.2782436009718498e-08</v>
       </c>
       <c r="F5" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75000037404808595</v>
       </c>
       <c r="G5" s="0">
-        <v>37.108333333333299</v>
+        <v>18.699227172577501</v>
       </c>
       <c r="H5" s="0">
-        <v>-0.123978190677758</v>
+        <v>9.7224264282238395e-07</v>
       </c>
       <c r="I5" s="0">
-        <v>-583.46484614639701</v>
+        <v>0.82898490473446595</v>
       </c>
       <c r="J5" s="0">
-        <v>329.50364539382798</v>
+        <v>22.053387600867499</v>
       </c>
       <c r="K5" s="0">
-        <v>-0.39710585104502683</v>
+        <v>-0.54218260236770977</v>
       </c>
       <c r="L5" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.75000033126564991</v>
       </c>
       <c r="M5" s="0">
-        <v>583.3408679557192</v>
+        <v>-0.82898393249182312</v>
       </c>
       <c r="N5" s="0">
         <v>1</v>
@@ -344,40 +344,40 @@
         <v>893</v>
       </c>
       <c r="B6" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C6" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D6" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E6" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F6" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G6" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H6" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I6" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J6" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K6" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L6" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M6" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N6" s="0">
         <v>1</v>
@@ -388,40 +388,40 @@
         <v>974</v>
       </c>
       <c r="B7" s="0">
-        <v>0.113428840416073</v>
+        <v>0.11342883987746</v>
       </c>
       <c r="C7" s="0">
-        <v>0.25031443117236202</v>
+        <v>0.79494555600145</v>
       </c>
       <c r="D7" s="0">
-        <v>1.84772540430773</v>
+        <v>1.8477254363569899</v>
       </c>
       <c r="E7" s="0">
-        <v>0.32225219439250502</v>
+        <v>0.32224342361686598</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.52178531009246498</v>
+        <v>0.74888683224942398</v>
       </c>
       <c r="G7" s="0">
-        <v>1.5511855577145599</v>
+        <v>1.5511551737552101</v>
       </c>
       <c r="H7" s="0">
-        <v>0.22670059173009799</v>
+        <v>0.226708185832589</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.68452563240022102</v>
+        <v>0.78845431372007901</v>
       </c>
       <c r="J7" s="0">
-        <v>1.75570299001483</v>
+        <v>1.7556762722160799</v>
       </c>
       <c r="K7" s="0">
-        <v>-0.13688559075628903</v>
+        <v>-0.68151671612399001</v>
       </c>
       <c r="L7" s="0">
-        <v>0.84403750448496995</v>
+        <v>-0.42664340863255801</v>
       </c>
       <c r="M7" s="0">
-        <v>0.91122622413031906</v>
+        <v>-0.56174612788749001</v>
       </c>
       <c r="N7" s="0">
         <v>1</v>
@@ -432,40 +432,40 @@
         <v>1019</v>
       </c>
       <c r="B8" s="0">
-        <v>0.49999983863143499</v>
+        <v>0.60556729637479301</v>
       </c>
       <c r="C8" s="0">
-        <v>0.25009458576326199</v>
+        <v>0.659449238074578</v>
       </c>
       <c r="D8" s="0">
-        <v>1.02527319361708</v>
+        <v>0.941453441986705</v>
       </c>
       <c r="E8" s="0">
-        <v>1.51521643470344</v>
+        <v>1.49999545794486</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.9019715924056899</v>
+        <v>0.75013163685165796</v>
       </c>
       <c r="G8" s="0">
-        <v>1.32606777499458</v>
+        <v>1.3341916705091099</v>
       </c>
       <c r="H8" s="0">
-        <v>4472583249713.6699</v>
+        <v>1.4999994899506399</v>
       </c>
       <c r="I8" s="0">
-        <v>-4961489673391.5596</v>
+        <v>0.88568205542998901</v>
       </c>
       <c r="J8" s="0">
-        <v>3.3863869843052701</v>
+        <v>4.2978516742179904</v>
       </c>
       <c r="K8" s="0">
-        <v>0.249905252868173</v>
+        <v>-0.053881941699784996</v>
       </c>
       <c r="L8" s="0">
-        <v>3.4171880271091299</v>
+        <v>0.74986382109320204</v>
       </c>
       <c r="M8" s="0">
-        <v>9434072923105.2305</v>
+        <v>0.61431743452065091</v>
       </c>
       <c r="N8" s="0">
         <v>1</v>
@@ -476,40 +476,40 @@
         <v>1083</v>
       </c>
       <c r="B9" s="0">
-        <v>0.12960992129295101</v>
+        <v>0.129609932485519</v>
       </c>
       <c r="C9" s="0">
-        <v>0.24999746537279499</v>
+        <v>0.74977400789802695</v>
       </c>
       <c r="D9" s="0">
-        <v>0.87529898156397501</v>
+        <v>0.87529899990990501</v>
       </c>
       <c r="E9" s="0">
-        <v>0.22935809120817</v>
+        <v>0.22936153257077899</v>
       </c>
       <c r="F9" s="0">
-        <v>0.40469515680122697</v>
+        <v>0.65165740736606304</v>
       </c>
       <c r="G9" s="0">
-        <v>0.70972475740239704</v>
+        <v>0.70973844951202403</v>
       </c>
       <c r="H9" s="0">
-        <v>0.18686311395156399</v>
+        <v>0.18687960171707699</v>
       </c>
       <c r="I9" s="0">
-        <v>0.18325384871039399</v>
+        <v>0.75003367036566504</v>
       </c>
       <c r="J9" s="0">
-        <v>0.85047221985509303</v>
+        <v>0.85048484784663003</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.12038754407984398</v>
+        <v>-0.62016407541250795</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.17533706559305698</v>
+        <v>-0.42229587479528408</v>
       </c>
       <c r="M9" s="0">
-        <v>0.003609265241170001</v>
+        <v>-0.56315406864858808</v>
       </c>
       <c r="N9" s="0">
         <v>1</v>
@@ -520,40 +520,40 @@
         <v>1126</v>
       </c>
       <c r="B10" s="0">
-        <v>8.8114300770314295e-09</v>
+        <v>4.4052836417970901e-08</v>
       </c>
       <c r="C10" s="0">
-        <v>0.254744830617538</v>
+        <v>0.72740860631915705</v>
       </c>
       <c r="D10" s="0">
-        <v>2.0229475769395302</v>
+        <v>2.0229480582932902</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.49245714188780099</v>
+        <v>1.3939360037888201e-07</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.75553161103769295</v>
+        <v>0.73997842809192804</v>
       </c>
       <c r="G10" s="0">
-        <v>1.64328394920224</v>
+        <v>2.0229480037968299</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.137647647638483</v>
+        <v>1.8279314625486201e-07</v>
       </c>
       <c r="I10" s="0">
-        <v>-2.07506836932003</v>
+        <v>0.75420496552433702</v>
       </c>
       <c r="J10" s="0">
-        <v>1.5974693853615201</v>
+        <v>2.02294840404684</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.25474482180610791</v>
+        <v>-0.72740856226632067</v>
       </c>
       <c r="L10" s="0">
-        <v>0.26307446914989197</v>
+        <v>-0.73997828869832771</v>
       </c>
       <c r="M10" s="0">
-        <v>1.9374207216815471</v>
+        <v>-0.75420478273119074</v>
       </c>
       <c r="N10" s="0">
         <v>0</v>
@@ -564,40 +564,40 @@
         <v>1252</v>
       </c>
       <c r="B11" s="0">
-        <v>2.2894359655331701e-08</v>
+        <v>2.30445503006963e-08</v>
       </c>
       <c r="C11" s="0">
-        <v>0.246338955764657</v>
+        <v>0.64164273869541699</v>
       </c>
       <c r="D11" s="0">
-        <v>0.88857847434312298</v>
+        <v>0.88857804990725697</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.52412416079120105</v>
+        <v>2.73779270002803e-07</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.19070617989011501</v>
+        <v>0.64390596992786497</v>
       </c>
       <c r="G11" s="0">
-        <v>0.65638468787789594</v>
+        <v>0.88857839923021698</v>
       </c>
       <c r="H11" s="0">
-        <v>-0.034932318849057599</v>
+        <v>1.20706725763027e-07</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.84435354041022004</v>
+        <v>0.64900251219054395</v>
       </c>
       <c r="J11" s="0">
-        <v>0.82618045744234403</v>
+        <v>0.88857820825383005</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.24633893287029734</v>
+        <v>-0.64164271565086672</v>
       </c>
       <c r="L11" s="0">
-        <v>-0.33341798090108604</v>
+        <v>-0.64390569614859494</v>
       </c>
       <c r="M11" s="0">
-        <v>0.80942122156116247</v>
+        <v>-0.64900239148381822</v>
       </c>
       <c r="N11" s="0">
         <v>1</v>
@@ -608,40 +608,40 @@
         <v>1363</v>
       </c>
       <c r="B12" s="0">
-        <v>7.5163280974983394e-08</v>
+        <v>3.7581493257582901e-07</v>
       </c>
       <c r="C12" s="0">
-        <v>0.25921821412638202</v>
+        <v>0.68542821525213005</v>
       </c>
       <c r="D12" s="0">
-        <v>0.52367082211496196</v>
+        <v>0.52367077572008203</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.48443691129879801</v>
+        <v>1.7590962965583699e-07</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.064972143414759001</v>
+        <v>0.69449302505466504</v>
       </c>
       <c r="G12" s="0">
-        <v>0.40839073422967898</v>
+        <v>0.52367070100936497</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.068333346616979707</v>
+        <v>1.3620310610974199e-07</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.093229677405088904</v>
+        <v>0.69915655628280005</v>
       </c>
       <c r="J12" s="0">
-        <v>0.46555571793300898</v>
+        <v>0.52367076921758304</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.25921813896310103</v>
+        <v>-0.68542783943719743</v>
       </c>
       <c r="L12" s="0">
-        <v>-0.41946476788403902</v>
+        <v>-0.6944928491450354</v>
       </c>
       <c r="M12" s="0">
-        <v>0.024896330788109197</v>
+        <v>-0.69915642007969392</v>
       </c>
       <c r="N12" s="0">
         <v>0</v>
@@ -652,40 +652,40 @@
         <v>1423</v>
       </c>
       <c r="B13" s="0">
-        <v>3.2366666370707699e-09</v>
+        <v>1.5952673059291501e-08</v>
       </c>
       <c r="C13" s="0">
-        <v>0.38135027967826801</v>
+        <v>0.75000000000060596</v>
       </c>
       <c r="D13" s="0">
-        <v>19.1021060323325</v>
+        <v>18.896257422988299</v>
       </c>
       <c r="E13" s="0">
-        <v>-0.0291832758410164</v>
+        <v>2.4852722597534599e-10</v>
       </c>
       <c r="F13" s="0">
-        <v>-57.180692490296302</v>
+        <v>0.48458125813066499</v>
       </c>
       <c r="G13" s="0">
-        <v>28.306542874514999</v>
+        <v>40.197494988897297</v>
       </c>
       <c r="H13" s="0">
-        <v>-0.0864898289756732</v>
+        <v>2.79598968279515e-07</v>
       </c>
       <c r="I13" s="0">
-        <v>-12.5542870448838</v>
+        <v>0.824263607421995</v>
       </c>
       <c r="J13" s="0">
-        <v>7.4379126338683701</v>
+        <v>21.264634797497902</v>
       </c>
       <c r="K13" s="0">
-        <v>-0.38135027644160135</v>
+        <v>-0.74999998404793289</v>
       </c>
       <c r="L13" s="0">
-        <v>57.151509214455288</v>
+        <v>-0.48458125788213779</v>
       </c>
       <c r="M13" s="0">
-        <v>12.467797215908128</v>
+        <v>-0.82426332782302669</v>
       </c>
       <c r="N13" s="0">
         <v>1</v>
@@ -696,40 +696,40 @@
         <v>1499</v>
       </c>
       <c r="B14" s="0">
-        <v>0.099369123807290793</v>
+        <v>0.099369137579821507</v>
       </c>
       <c r="C14" s="0">
-        <v>0.25020579781635899</v>
+        <v>0.75003007585132697</v>
       </c>
       <c r="D14" s="0">
-        <v>0.85378316176425195</v>
+        <v>0.85378320632976701</v>
       </c>
       <c r="E14" s="0">
-        <v>0.394455976188406</v>
+        <v>0.39444564835421803</v>
       </c>
       <c r="F14" s="0">
-        <v>-0.42483399305281599</v>
+        <v>0.66583519730026797</v>
       </c>
       <c r="G14" s="0">
-        <v>0.96265663167167903</v>
+        <v>0.96267102491982404</v>
       </c>
       <c r="H14" s="0">
-        <v>0.62534591698731401</v>
+        <v>0.62537863206203803</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.59813917580603704</v>
+        <v>0.77253513419193598</v>
       </c>
       <c r="J14" s="0">
-        <v>1.61317067211684</v>
+        <v>1.61318182695495</v>
       </c>
       <c r="K14" s="0">
-        <v>-0.15083667400906819</v>
+        <v>-0.65066093827150551</v>
       </c>
       <c r="L14" s="0">
-        <v>0.81928996924122199</v>
+        <v>-0.27138954894604994</v>
       </c>
       <c r="M14" s="0">
-        <v>1.2234850927933509</v>
+        <v>-0.14715650212989795</v>
       </c>
       <c r="N14" s="0">
         <v>0</v>
@@ -740,40 +740,40 @@
         <v>1867</v>
       </c>
       <c r="B15" s="0">
-        <v>0.14818349902867101</v>
+        <v>0.74387808732830096</v>
       </c>
       <c r="C15" s="0">
-        <v>0.24332873567881799</v>
+        <v>0.803851400593247</v>
       </c>
       <c r="D15" s="0">
-        <v>1.98150711380461e-08</v>
+        <v>2.4378440275216903e-07</v>
       </c>
       <c r="E15" s="0">
-        <v>0.69227733568737904</v>
+        <v>0.54273661573682896</v>
       </c>
       <c r="F15" s="0">
-        <v>0.094512907969787202</v>
+        <v>0.74679975215026295</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.32098746517533699</v>
+        <v>6.8700431758582102e-08</v>
       </c>
       <c r="H15" s="0">
-        <v>7380264246505.4404</v>
+        <v>0.67098406731390503</v>
       </c>
       <c r="I15" s="0">
-        <v>-7761586541254.1797</v>
+        <v>0.74865830007288203</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.38644615306696101</v>
+        <v>9.5357155324614397e-08</v>
       </c>
       <c r="K15" s="0">
-        <v>-0.095145236650146986</v>
+        <v>-0.059973313264946038</v>
       </c>
       <c r="L15" s="0">
-        <v>0.59776442771759186</v>
+        <v>-0.20406313641343399</v>
       </c>
       <c r="M15" s="0">
-        <v>15141850787759.621</v>
+        <v>-0.077674232758977002</v>
       </c>
       <c r="N15" s="0">
         <v>0</v>
@@ -784,40 +784,40 @@
         <v>1870</v>
       </c>
       <c r="B16" s="0">
-        <v>0.25264814862871698</v>
+        <v>0.25264816119067302</v>
       </c>
       <c r="C16" s="0">
-        <v>0.24969126765848501</v>
+        <v>0.74518863868254204</v>
       </c>
       <c r="D16" s="0">
-        <v>0.88309694577479003</v>
+        <v>0.88309686899167805</v>
       </c>
       <c r="E16" s="0">
-        <v>0.78863736870609602</v>
+        <v>0.78858873503708704</v>
       </c>
       <c r="F16" s="0">
-        <v>-0.70420897103746005</v>
+        <v>0.72978216408624597</v>
       </c>
       <c r="G16" s="0">
-        <v>1.1249286863901999</v>
+        <v>1.1249407048292299</v>
       </c>
       <c r="H16" s="0">
-        <v>1.45271219237041</v>
+        <v>1.45269810595625</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.95580412397595604</v>
+        <v>0.75060382105502099</v>
       </c>
       <c r="J16" s="0">
-        <v>2.48279458540354</v>
+        <v>2.4827981779582702</v>
       </c>
       <c r="K16" s="0">
-        <v>0.0029568809702319732</v>
+        <v>-0.49254047749186902</v>
       </c>
       <c r="L16" s="0">
-        <v>1.4928463397435561</v>
+        <v>0.058806570950841075</v>
       </c>
       <c r="M16" s="0">
-        <v>2.4085163163463661</v>
+        <v>0.70209428490122905</v>
       </c>
       <c r="N16" s="0">
         <v>1</v>
@@ -828,40 +828,40 @@
         <v>2397</v>
       </c>
       <c r="B17" s="0">
-        <v>0.16204712145837599</v>
+        <v>0.16204711558815199</v>
       </c>
       <c r="C17" s="0">
-        <v>0.24997920264567899</v>
+        <v>0.750219816557403</v>
       </c>
       <c r="D17" s="0">
-        <v>1.7268036992504701</v>
+        <v>1.72680396540338</v>
       </c>
       <c r="E17" s="0">
-        <v>0.51356261652556601</v>
+        <v>0.51356929311049604</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.637078354499658</v>
+        <v>0.76858832430716495</v>
       </c>
       <c r="G17" s="0">
-        <v>1.7464275928073001</v>
+        <v>1.7464004779098099</v>
       </c>
       <c r="H17" s="0">
-        <v>0.47244825673496599</v>
+        <v>0.47245114192401899</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.77568479621090702</v>
+        <v>0.78019460539242202</v>
       </c>
       <c r="J17" s="0">
-        <v>2.1891460491451098</v>
+        <v>2.1891304252883299</v>
       </c>
       <c r="K17" s="0">
-        <v>-0.087932081187303002</v>
+        <v>-0.58817270096925101</v>
       </c>
       <c r="L17" s="0">
-        <v>1.1506409710252239</v>
+        <v>-0.25501903119666891</v>
       </c>
       <c r="M17" s="0">
-        <v>1.248133052945873</v>
+        <v>-0.30774346346840303</v>
       </c>
       <c r="N17" s="0">
         <v>0</v>
@@ -872,40 +872,40 @@
         <v>2411</v>
       </c>
       <c r="B18" s="0">
-        <v>7.3668412816490599e-09</v>
+        <v>7.3671850440461898e-09</v>
       </c>
       <c r="C18" s="0">
-        <v>0.22837573780943901</v>
+        <v>0.69746763625818897</v>
       </c>
       <c r="D18" s="0">
-        <v>1.56262011894473</v>
+        <v>1.56262260675607</v>
       </c>
       <c r="E18" s="0">
-        <v>-1.2523020839005301</v>
+        <v>2.3611085994004899e-08</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.072326420357909593</v>
+        <v>0.68886063462698499</v>
       </c>
       <c r="G18" s="0">
-        <v>1.09526805556587</v>
+        <v>1.56262287528355</v>
       </c>
       <c r="H18" s="0">
-        <v>-0.249999999075737</v>
+        <v>9.6433815132160095e-08</v>
       </c>
       <c r="I18" s="0">
-        <v>-1.1060898485352599</v>
+        <v>0.75686635236947197</v>
       </c>
       <c r="J18" s="0">
-        <v>1.2082639065176299</v>
+        <v>1.56262431488816</v>
       </c>
       <c r="K18" s="0">
-        <v>-0.22837573044259774</v>
+        <v>-0.69746762889100389</v>
       </c>
       <c r="L18" s="0">
-        <v>-1.1799756635426206</v>
+        <v>-0.68886061101589902</v>
       </c>
       <c r="M18" s="0">
-        <v>0.85608984945952293</v>
+        <v>-0.75686625593565682</v>
       </c>
       <c r="N18" s="0">
         <v>1</v>
@@ -916,40 +916,40 @@
         <v>2431</v>
       </c>
       <c r="B19" s="0">
-        <v>0.013163271077651899</v>
+        <v>0.0131633310359262</v>
       </c>
       <c r="C19" s="0">
-        <v>0.25002778683411703</v>
+        <v>0.750124776678736</v>
       </c>
       <c r="D19" s="0">
-        <v>1.16208922494881</v>
+        <v>1.1620894362469201</v>
       </c>
       <c r="E19" s="0">
-        <v>0.14674867880817799</v>
+        <v>0.146749889747993</v>
       </c>
       <c r="F19" s="0">
-        <v>-0.746651937189453</v>
+        <v>0.74921898214591298</v>
       </c>
       <c r="G19" s="0">
-        <v>1.30183937260886</v>
+        <v>1.30182613088739</v>
       </c>
       <c r="H19" s="0">
-        <v>0.233682362194818</v>
+        <v>0.233687705058581</v>
       </c>
       <c r="I19" s="0">
-        <v>-3.1015192597007801</v>
+        <v>0.75234747130711199</v>
       </c>
       <c r="J19" s="0">
-        <v>1.72887586005814</v>
+        <v>1.7288572382621601</v>
       </c>
       <c r="K19" s="0">
-        <v>-0.23686451575646514</v>
+        <v>-0.73696144564280985</v>
       </c>
       <c r="L19" s="0">
-        <v>0.89340061599763099</v>
+        <v>-0.60246909239792001</v>
       </c>
       <c r="M19" s="0">
-        <v>3.3352016218955982</v>
+        <v>-0.51865976624853105</v>
       </c>
       <c r="N19" s="0">
         <v>1</v>
@@ -960,40 +960,40 @@
         <v>2690</v>
       </c>
       <c r="B20" s="0">
-        <v>0.061235908771062997</v>
+        <v>0.0612359156536008</v>
       </c>
       <c r="C20" s="0">
-        <v>0.24999422723015999</v>
+        <v>0.74979097024663799</v>
       </c>
       <c r="D20" s="0">
-        <v>1.5336188048969599</v>
+        <v>1.5336188997757401</v>
       </c>
       <c r="E20" s="0">
-        <v>0.22530215033141199</v>
+        <v>0.225302708158962</v>
       </c>
       <c r="F20" s="0">
-        <v>0.293532373914624</v>
+        <v>0.749756915917422</v>
       </c>
       <c r="G20" s="0">
-        <v>1.61131768915371</v>
+        <v>1.6113208755564501</v>
       </c>
       <c r="H20" s="0">
-        <v>0.27689351555851199</v>
+        <v>0.27689334615946698</v>
       </c>
       <c r="I20" s="0">
-        <v>-1.2452092440552101</v>
+        <v>0.749979194487019</v>
       </c>
       <c r="J20" s="0">
-        <v>2.3988502334597599</v>
+        <v>2.3988802508237601</v>
       </c>
       <c r="K20" s="0">
-        <v>-0.18875831845909699</v>
+        <v>-0.68855505459303723</v>
       </c>
       <c r="L20" s="0">
-        <v>-0.068230223583212013</v>
+        <v>-0.52445420775845997</v>
       </c>
       <c r="M20" s="0">
-        <v>1.522102759613722</v>
+        <v>-0.47308584832755202</v>
       </c>
       <c r="N20" s="0">
         <v>0</v>
@@ -1004,40 +1004,40 @@
         <v>2803</v>
       </c>
       <c r="B21" s="0">
-        <v>0.499999960228247</v>
+        <v>1.4999999835413</v>
       </c>
       <c r="C21" s="0">
-        <v>0.249957577103644</v>
+        <v>0.76192610033235597</v>
       </c>
       <c r="D21" s="0">
-        <v>0.475242287308902</v>
+        <v>0.32765817680627701</v>
       </c>
       <c r="E21" s="0">
-        <v>-21.344098297475899</v>
+        <v>1.49999997576834</v>
       </c>
       <c r="F21" s="0">
-        <v>23.876576938506101</v>
+        <v>0.76278226756298095</v>
       </c>
       <c r="G21" s="0">
-        <v>-0.047859753450036797</v>
+        <v>0.51156264318104405</v>
       </c>
       <c r="H21" s="0">
-        <v>-0.25014273721628699</v>
+        <v>1.4999989652484</v>
       </c>
       <c r="I21" s="0">
-        <v>0.30038264576331503</v>
+        <v>0.74597952017370295</v>
       </c>
       <c r="J21" s="0">
-        <v>-0.40529558839172503</v>
+        <v>0.28269548592272697</v>
       </c>
       <c r="K21" s="0">
-        <v>0.25004238312460303</v>
+        <v>0.73807388320894407</v>
       </c>
       <c r="L21" s="0">
-        <v>-45.220675235982</v>
+        <v>0.73721770820535903</v>
       </c>
       <c r="M21" s="0">
-        <v>-0.55052538297960196</v>
+        <v>0.75401944507469709</v>
       </c>
       <c r="N21" s="0">
         <v>0</v>
@@ -1048,40 +1048,40 @@
         <v>2854</v>
       </c>
       <c r="B22" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C22" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D22" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E22" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F22" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G22" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H22" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I22" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J22" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K22" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L22" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M22" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N22" s="0">
         <v>0</v>
@@ -1092,40 +1092,40 @@
         <v>2899</v>
       </c>
       <c r="B23" s="0">
-        <v>0.051006854424783601</v>
+        <v>0.051006884347871699</v>
       </c>
       <c r="C23" s="0">
-        <v>0.24975186133840799</v>
+        <v>0.75004780102420299</v>
       </c>
       <c r="D23" s="0">
-        <v>0.836883528582689</v>
+        <v>0.83688345300962197</v>
       </c>
       <c r="E23" s="0">
-        <v>0.26109530892498101</v>
+        <v>0.26110064455349002</v>
       </c>
       <c r="F23" s="0">
-        <v>0.43431000430575101</v>
+        <v>0.70015767517406302</v>
       </c>
       <c r="G23" s="0">
-        <v>0.93551389494568404</v>
+        <v>0.93554060789458904</v>
       </c>
       <c r="H23" s="0">
-        <v>0.65644446435420201</v>
+        <v>0.65641664071680095</v>
       </c>
       <c r="I23" s="0">
-        <v>1.2374747338571099</v>
+        <v>0.75767539834301501</v>
       </c>
       <c r="J23" s="0">
-        <v>1.42359085252006</v>
+        <v>1.4235793853903</v>
       </c>
       <c r="K23" s="0">
-        <v>-0.1987450069136244</v>
+        <v>-0.69904091667633128</v>
       </c>
       <c r="L23" s="0">
-        <v>-0.17321469538077</v>
+        <v>-0.439057030620573</v>
       </c>
       <c r="M23" s="0">
-        <v>-0.58103026950290793</v>
+        <v>-0.10125875762621406</v>
       </c>
       <c r="N23" s="0">
         <v>0</v>
@@ -1136,40 +1136,40 @@
         <v>2959</v>
       </c>
       <c r="B24" s="0">
-        <v>0.078005419765296</v>
+        <v>0.078005432139063205</v>
       </c>
       <c r="C24" s="0">
-        <v>0.24986209848354299</v>
+        <v>0.74362462446794197</v>
       </c>
       <c r="D24" s="0">
-        <v>0.996871731590939</v>
+        <v>0.99687179239315804</v>
       </c>
       <c r="E24" s="0">
-        <v>0.34555020308464002</v>
+        <v>0.34556709438600802</v>
       </c>
       <c r="F24" s="0">
-        <v>-0.37164587848891001</v>
+        <v>0.75006361638920904</v>
       </c>
       <c r="G24" s="0">
-        <v>1.1570089501730001</v>
+        <v>1.1569694897946099</v>
       </c>
       <c r="H24" s="0">
-        <v>0.60228337290994205</v>
+        <v>0.602263339953376</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.13610888600001</v>
+        <v>0.78920073325850004</v>
       </c>
       <c r="J24" s="0">
-        <v>1.87933202579326</v>
+        <v>1.87934072970753</v>
       </c>
       <c r="K24" s="0">
-        <v>-0.171856678718247</v>
+        <v>-0.66561919232887878</v>
       </c>
       <c r="L24" s="0">
-        <v>0.71719608157355008</v>
+        <v>-0.40449652200320102</v>
       </c>
       <c r="M24" s="0">
-        <v>0.73839225890995208</v>
+        <v>-0.18693739330512404</v>
       </c>
       <c r="N24" s="0">
         <v>0</v>
@@ -1180,40 +1180,40 @@
         <v>2998</v>
       </c>
       <c r="B25" s="0">
-        <v>0.171231427417989</v>
+        <v>0.17123142816567999</v>
       </c>
       <c r="C25" s="0">
-        <v>0.25093187814905599</v>
+        <v>0.74982292563311803</v>
       </c>
       <c r="D25" s="0">
-        <v>1.2021202646554801</v>
+        <v>1.2021202494840999</v>
       </c>
       <c r="E25" s="0">
-        <v>0.601379473069654</v>
+        <v>0.60139701461621298</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.57310625151514805</v>
+        <v>0.75589796515111696</v>
       </c>
       <c r="G25" s="0">
-        <v>1.52164050885527</v>
+        <v>1.52165752537771</v>
       </c>
       <c r="H25" s="0">
-        <v>0.90840139555822996</v>
+        <v>0.90839905560329504</v>
       </c>
       <c r="I25" s="0">
-        <v>-1.0061684223038401</v>
+        <v>0.74569510682196705</v>
       </c>
       <c r="J25" s="0">
-        <v>2.6933958569320602</v>
+        <v>2.6933652288666901</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.079700450731066991</v>
+        <v>-0.57859149746743799</v>
       </c>
       <c r="L25" s="0">
-        <v>1.1744857245848022</v>
+        <v>-0.15450095053490398</v>
       </c>
       <c r="M25" s="0">
-        <v>1.91456981786207</v>
+        <v>0.16270394878132799</v>
       </c>
       <c r="N25" s="0">
         <v>0</v>
@@ -1224,40 +1224,40 @@
         <v>3103</v>
       </c>
       <c r="B26" s="0">
-        <v>0.049133744525234099</v>
+        <v>0.049133743756610303</v>
       </c>
       <c r="C26" s="0">
-        <v>0.24931128951283499</v>
+        <v>0.76981014011691196</v>
       </c>
       <c r="D26" s="0">
-        <v>2.2159223463672202</v>
+        <v>2.2159223794415501</v>
       </c>
       <c r="E26" s="0">
-        <v>0.14946834258153499</v>
+        <v>0.149468680337557</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.53164269602202996</v>
+        <v>0.75001568564908205</v>
       </c>
       <c r="G26" s="0">
-        <v>2.1724906011217699</v>
+        <v>2.1724477713288599</v>
       </c>
       <c r="H26" s="0">
-        <v>0.165585640128774</v>
+        <v>0.16558488599145599</v>
       </c>
       <c r="I26" s="0">
-        <v>-2.6473543449970398</v>
+        <v>0.75899775803842995</v>
       </c>
       <c r="J26" s="0">
-        <v>2.7658602161544801</v>
+        <v>2.7658410065181398</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.20017754498760088</v>
+        <v>-0.72067639636030167</v>
       </c>
       <c r="L26" s="0">
-        <v>0.68111103860356492</v>
+        <v>-0.60054700531152505</v>
       </c>
       <c r="M26" s="0">
-        <v>2.8129399851258139</v>
+        <v>-0.59341287204697402</v>
       </c>
       <c r="N26" s="0">
         <v>1</v>
@@ -1268,40 +1268,40 @@
         <v>3178</v>
       </c>
       <c r="B27" s="0">
-        <v>6.5297233507041002e-09</v>
+        <v>6.5293568152999798e-09</v>
       </c>
       <c r="C27" s="0">
-        <v>0.24852820164897901</v>
+        <v>0.69398080502041104</v>
       </c>
       <c r="D27" s="0">
-        <v>1.5874006539995</v>
+        <v>1.58740096354192</v>
       </c>
       <c r="E27" s="0">
-        <v>-0.91681932817594203</v>
+        <v>5.1667927837178696e-09</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.55152342271786403</v>
+        <v>0.56233882018185799</v>
       </c>
       <c r="G27" s="0">
-        <v>1.1313071340013701</v>
+        <v>1.5874009536806499</v>
       </c>
       <c r="H27" s="0">
-        <v>-0.204114136285235</v>
+        <v>4.7777422346794599e-09</v>
       </c>
       <c r="I27" s="0">
-        <v>-1.0208018020185801</v>
+        <v>0.58738199020821802</v>
       </c>
       <c r="J27" s="0">
-        <v>1.0958694169645999</v>
+        <v>1.58740087547333</v>
       </c>
       <c r="K27" s="0">
-        <v>-0.24852819511925567</v>
+        <v>-0.69398079849105421</v>
       </c>
       <c r="L27" s="0">
-        <v>-0.365295905458078</v>
+        <v>-0.56233881501506522</v>
       </c>
       <c r="M27" s="0">
-        <v>0.81668766573334506</v>
+        <v>-0.58738198543047582</v>
       </c>
       <c r="N27" s="0">
         <v>1</v>
@@ -1312,40 +1312,40 @@
         <v>3210</v>
       </c>
       <c r="B28" s="0">
-        <v>6.7363493809431397e-09</v>
+        <v>6.7363492726379502e-09</v>
       </c>
       <c r="C28" s="0">
-        <v>0.24983152814413501</v>
+        <v>0.71791341177232304</v>
       </c>
       <c r="D28" s="0">
-        <v>1.79395645789696</v>
+        <v>1.7939565610414001</v>
       </c>
       <c r="E28" s="0">
-        <v>-0.67439516201426297</v>
+        <v>1.17013053289614e-07</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.37722753165425399</v>
+        <v>0.67065160999227802</v>
       </c>
       <c r="G28" s="0">
-        <v>1.3748286878465801</v>
+        <v>1.7939555383224499</v>
       </c>
       <c r="H28" s="0">
-        <v>-0.233098560134434</v>
+        <v>1.0879324474347e-07</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.20154899460192</v>
+        <v>0.63325764730259204</v>
       </c>
       <c r="J28" s="0">
-        <v>1.23857277886647</v>
+        <v>1.79395695864961</v>
       </c>
       <c r="K28" s="0">
-        <v>-0.24983152140778564</v>
+        <v>-0.71791340503597378</v>
       </c>
       <c r="L28" s="0">
-        <v>-0.29716763036000898</v>
+        <v>-0.67065149297922477</v>
       </c>
       <c r="M28" s="0">
-        <v>0.96845043446748602</v>
+        <v>-0.6332575385093473</v>
       </c>
       <c r="N28" s="0">
         <v>1</v>
@@ -1356,40 +1356,40 @@
         <v>3228</v>
       </c>
       <c r="B29" s="0">
-        <v>5.7791848190054401e-09</v>
+        <v>5.77955831579689e-09</v>
       </c>
       <c r="C29" s="0">
-        <v>0.25096767952907001</v>
+        <v>0.72649680854891996</v>
       </c>
       <c r="D29" s="0">
-        <v>2.1815823965894601</v>
+        <v>2.1815822022548002</v>
       </c>
       <c r="E29" s="0">
-        <v>-0.41146526762698299</v>
+        <v>9.9193866419321594e-08</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.43275109679158102</v>
+        <v>0.740068235893791</v>
       </c>
       <c r="G29" s="0">
-        <v>1.7679157000674599</v>
+        <v>2.18158258172289</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.20045544884111799</v>
+        <v>8.5693970261752196e-08</v>
       </c>
       <c r="I29" s="0">
-        <v>-1.94895600808901</v>
+        <v>0.758512830999721</v>
       </c>
       <c r="J29" s="0">
-        <v>1.6142179623667801</v>
+        <v>2.1815828151301102</v>
       </c>
       <c r="K29" s="0">
-        <v>-0.25096767374988521</v>
+        <v>-0.72649680276936168</v>
       </c>
       <c r="L29" s="0">
-        <v>0.021285829164598036</v>
+        <v>-0.74006813669992455</v>
       </c>
       <c r="M29" s="0">
-        <v>1.7485005592478919</v>
+        <v>-0.75851274530575075</v>
       </c>
       <c r="N29" s="0">
         <v>1</v>
@@ -1400,40 +1400,40 @@
         <v>3472</v>
       </c>
       <c r="B30" s="0">
-        <v>5.8206426998213603e-09</v>
+        <v>1.6494998014038299e-07</v>
       </c>
       <c r="C30" s="0">
-        <v>0.35406011282662597</v>
+        <v>0.74998635154729298</v>
       </c>
       <c r="D30" s="0">
-        <v>19.5712942991379</v>
+        <v>17.320417932444101</v>
       </c>
       <c r="E30" s="0">
-        <v>-0.017166951499471599</v>
+        <v>3.8502878033290298e-07</v>
       </c>
       <c r="F30" s="0">
-        <v>-22.6999890749054</v>
+        <v>0.75000545510066396</v>
       </c>
       <c r="G30" s="0">
-        <v>28.267659571909999</v>
+        <v>17.3148924716698</v>
       </c>
       <c r="H30" s="0">
-        <v>-0.00064585202881470803</v>
+        <v>7.0267567775860404e-08</v>
       </c>
       <c r="I30" s="0">
-        <v>-701.620264702957</v>
+        <v>0.76871867035260799</v>
       </c>
       <c r="J30" s="0">
-        <v>725.51297207615198</v>
+        <v>18.9744337063036</v>
       </c>
       <c r="K30" s="0">
-        <v>-0.35406010700598328</v>
+        <v>-0.74998618659731286</v>
       </c>
       <c r="L30" s="0">
-        <v>22.682822123405927</v>
+        <v>-0.75000507007188366</v>
       </c>
       <c r="M30" s="0">
-        <v>701.61961885092819</v>
+        <v>-0.76871860008504023</v>
       </c>
       <c r="N30" s="0">
         <v>0</v>
@@ -1444,40 +1444,40 @@
         <v>3624</v>
       </c>
       <c r="B31" s="0">
-        <v>0.13935902729903801</v>
+        <v>0.13935902592309601</v>
       </c>
       <c r="C31" s="0">
-        <v>0.250046903471766</v>
+        <v>0.75348126892574696</v>
       </c>
       <c r="D31" s="0">
-        <v>1.5711362374642199</v>
+        <v>1.5711363177374</v>
       </c>
       <c r="E31" s="0">
-        <v>0.49257689634470297</v>
+        <v>0.49257059571853201</v>
       </c>
       <c r="F31" s="0">
-        <v>-0.722396110837914</v>
+        <v>0.774024768205678</v>
       </c>
       <c r="G31" s="0">
-        <v>1.8432606597841401</v>
+        <v>1.8432487541757001</v>
       </c>
       <c r="H31" s="0">
-        <v>0.47140851115416399</v>
+        <v>0.47140794632768201</v>
       </c>
       <c r="I31" s="0">
-        <v>-2.78862471442066</v>
+        <v>0.83083723126042497</v>
       </c>
       <c r="J31" s="0">
-        <v>2.1977957098272398</v>
+        <v>2.1978169809861701</v>
       </c>
       <c r="K31" s="0">
-        <v>-0.11068787617272799</v>
+        <v>-0.61412224300265095</v>
       </c>
       <c r="L31" s="0">
-        <v>1.214973007182617</v>
+        <v>-0.28145417248714599</v>
       </c>
       <c r="M31" s="0">
-        <v>3.2600332255748241</v>
+        <v>-0.35942928493274295</v>
       </c>
       <c r="N31" s="0">
         <v>0</v>
@@ -1488,40 +1488,40 @@
         <v>3771</v>
       </c>
       <c r="B32" s="0">
-        <v>6.7574358849660301e-09</v>
+        <v>6.7870518567598703e-09</v>
       </c>
       <c r="C32" s="0">
-        <v>0.23290135742735499</v>
+        <v>0.55254629579725301</v>
       </c>
       <c r="D32" s="0">
-        <v>1.5328465811474701</v>
+        <v>1.5328463884967101</v>
       </c>
       <c r="E32" s="0">
-        <v>-0.94472863270247898</v>
+        <v>2.1588898278662401e-08</v>
       </c>
       <c r="F32" s="0">
-        <v>-0.43989694747401198</v>
+        <v>0.59767149880563997</v>
       </c>
       <c r="G32" s="0">
-        <v>1.08479619692027</v>
+        <v>1.5328481246510599</v>
       </c>
       <c r="H32" s="0">
-        <v>-0.206754711575799</v>
+        <v>4.9931702092665197e-07</v>
       </c>
       <c r="I32" s="0">
-        <v>-0.91476029280943905</v>
+        <v>0.605293726555025</v>
       </c>
       <c r="J32" s="0">
-        <v>1.03981739834625</v>
+        <v>1.5328501142356601</v>
       </c>
       <c r="K32" s="0">
-        <v>-0.2329013506699191</v>
+        <v>-0.5525462890102012</v>
       </c>
       <c r="L32" s="0">
-        <v>-0.504831685228467</v>
+        <v>-0.59767147721674174</v>
       </c>
       <c r="M32" s="0">
-        <v>0.7080055812336401</v>
+        <v>-0.60529322723800405</v>
       </c>
       <c r="N32" s="0">
         <v>1</v>
@@ -1532,40 +1532,40 @@
         <v>3928</v>
       </c>
       <c r="B33" s="0">
-        <v>5.5543492925180101e-09</v>
+        <v>1.11081411512809e-09</v>
       </c>
       <c r="C33" s="0">
-        <v>0.23331894349646301</v>
+        <v>0.74092980649498896</v>
       </c>
       <c r="D33" s="0">
-        <v>2.0445217952674102</v>
+        <v>2.0445212181933701</v>
       </c>
       <c r="E33" s="0">
-        <v>-22.983485765721699</v>
+        <v>1.7298491824418099e-08</v>
       </c>
       <c r="F33" s="0">
-        <v>23.041551398469402</v>
+        <v>0.73543923606995298</v>
       </c>
       <c r="G33" s="0">
-        <v>1.4748313859139299</v>
+        <v>2.0445213537737299</v>
       </c>
       <c r="H33" s="0">
-        <v>-0.24999999989575</v>
+        <v>3.5270034566143099e-08</v>
       </c>
       <c r="I33" s="0">
-        <v>-2.1087860707097401</v>
+        <v>1.1770777762298299</v>
       </c>
       <c r="J33" s="0">
-        <v>1.7737524188701099</v>
+        <v>2.0445199515104999</v>
       </c>
       <c r="K33" s="0">
-        <v>-0.23331893794211372</v>
+        <v>-0.74092980538417486</v>
       </c>
       <c r="L33" s="0">
-        <v>-46.025037164191104</v>
+        <v>-0.73543921877146112</v>
       </c>
       <c r="M33" s="0">
-        <v>1.8587860708139901</v>
+        <v>-1.1770777409597952</v>
       </c>
       <c r="N33" s="0">
         <v>1</v>
@@ -1576,40 +1576,40 @@
         <v>4164</v>
       </c>
       <c r="B34" s="0">
-        <v>9.4004441265420098e-09</v>
+        <v>9.4000068824264308e-09</v>
       </c>
       <c r="C34" s="0">
-        <v>0.22487500154228199</v>
+        <v>0.38316617720290203</v>
       </c>
       <c r="D34" s="0">
-        <v>0.98730026133593096</v>
+        <v>0.98730073269903296</v>
       </c>
       <c r="E34" s="0">
-        <v>-101.341723812995</v>
+        <v>2.81998361707054e-08</v>
       </c>
       <c r="F34" s="0">
-        <v>52.33005002614</v>
+        <v>0.61978139256518605</v>
       </c>
       <c r="G34" s="0">
-        <v>0.344171150170136</v>
+        <v>0.987300339899158</v>
       </c>
       <c r="H34" s="0">
-        <v>-0.24999999931427599</v>
+        <v>8.2100230129924797e-08</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.159269492717628</v>
+        <v>0.53090421557189804</v>
       </c>
       <c r="J34" s="0">
-        <v>0.77711370521396295</v>
+        <v>0.987300500291723</v>
       </c>
       <c r="K34" s="0">
-        <v>-0.22487499214183787</v>
+        <v>-0.38316616780289514</v>
       </c>
       <c r="L34" s="0">
-        <v>-153.671773839135</v>
+        <v>-0.61978136436534992</v>
       </c>
       <c r="M34" s="0">
-        <v>-0.090730506596647997</v>
+        <v>-0.53090413347166787</v>
       </c>
       <c r="N34" s="0">
         <v>0</v>
@@ -1620,40 +1620,40 @@
         <v>4231</v>
       </c>
       <c r="B35" s="0">
-        <v>1.65382764161532e-07</v>
+        <v>1.6538275206145001e-07</v>
       </c>
       <c r="C35" s="0">
-        <v>0.24944293206655499</v>
+        <v>0.74821756809908901</v>
       </c>
       <c r="D35" s="0">
-        <v>1.06872292659838</v>
+        <v>1.0687228556167601</v>
       </c>
       <c r="E35" s="0">
-        <v>-0.064666447418001996</v>
+        <v>2.9157755007078498e-07</v>
       </c>
       <c r="F35" s="0">
-        <v>0.61453499659247901</v>
+        <v>0.673946234024972</v>
       </c>
       <c r="G35" s="0">
-        <v>1.0181543817676599</v>
+        <v>1.0687226822336999</v>
       </c>
       <c r="H35" s="0">
-        <v>0.172792180028009</v>
+        <v>0.17279552263346201</v>
       </c>
       <c r="I35" s="0">
-        <v>0.45813507530937198</v>
+        <v>0.73546413684169398</v>
       </c>
       <c r="J35" s="0">
-        <v>1.5184217047967601</v>
+        <v>1.5184157208439499</v>
       </c>
       <c r="K35" s="0">
-        <v>-0.24944276668379084</v>
+        <v>-0.74821740271633697</v>
       </c>
       <c r="L35" s="0">
-        <v>-0.67920144401048099</v>
+        <v>-0.6739459424474219</v>
       </c>
       <c r="M35" s="0">
-        <v>-0.28534289528136297</v>
+        <v>-0.562668614208232</v>
       </c>
       <c r="N35" s="0">
         <v>0</v>
@@ -1664,40 +1664,40 @@
         <v>4241</v>
       </c>
       <c r="B36" s="0">
-        <v>6.0631667600781796e-09</v>
+        <v>6.0631092008949303e-09</v>
       </c>
       <c r="C36" s="0">
-        <v>0.24665056063701701</v>
+        <v>0.71725488786536096</v>
       </c>
       <c r="D36" s="0">
-        <v>2.6900041489805999</v>
+        <v>2.6900043877724502</v>
       </c>
       <c r="E36" s="0">
-        <v>-16.880158097985301</v>
+        <v>1.7340461590806099e-08</v>
       </c>
       <c r="F36" s="0">
-        <v>-8.7151302464656197</v>
+        <v>0.78367839346939305</v>
       </c>
       <c r="G36" s="0">
-        <v>2.0445211989406999</v>
+        <v>2.6900053084525601</v>
       </c>
       <c r="H36" s="0">
-        <v>-0.249999999956835</v>
+        <v>1.52445213012467e-08</v>
       </c>
       <c r="I36" s="0">
-        <v>-3.2550764429057102</v>
+        <v>0.90837722085821104</v>
       </c>
       <c r="J36" s="0">
-        <v>2.4205600198331099</v>
+        <v>2.6900043760194001</v>
       </c>
       <c r="K36" s="0">
-        <v>-0.24665055457385027</v>
+        <v>-0.71725488180225172</v>
       </c>
       <c r="L36" s="0">
-        <v>-8.1650278515196817</v>
+        <v>-0.78367837612893143</v>
       </c>
       <c r="M36" s="0">
-        <v>3.0050764429488752</v>
+        <v>-0.90837720561368973</v>
       </c>
       <c r="N36" s="0">
         <v>1</v>
@@ -1708,40 +1708,40 @@
         <v>4625</v>
       </c>
       <c r="B37" s="0">
-        <v>0.21766830096876999</v>
+        <v>0.67498033836444404</v>
       </c>
       <c r="C37" s="0">
-        <v>0.27262319784269901</v>
+        <v>0.79054952340387097</v>
       </c>
       <c r="D37" s="0">
-        <v>9.7350366176944904e-08</v>
+        <v>1.84428086170535e-06</v>
       </c>
       <c r="E37" s="0">
-        <v>0.30731970070727599</v>
+        <v>0.75156095725476502</v>
       </c>
       <c r="F37" s="0">
-        <v>0.21032222558202501</v>
+        <v>0.74995344605549696</v>
       </c>
       <c r="G37" s="0">
-        <v>-0.26904879709414498</v>
+        <v>4.4147073347883101e-07</v>
       </c>
       <c r="H37" s="0">
-        <v>0.46903608727060397</v>
+        <v>0.70590963439501497</v>
       </c>
       <c r="I37" s="0">
-        <v>0.18908745773993299</v>
+        <v>0.79727502578203102</v>
       </c>
       <c r="J37" s="0">
-        <v>-0.342638390253862</v>
+        <v>5.4518443340044695e-07</v>
       </c>
       <c r="K37" s="0">
-        <v>-0.054954896873929016</v>
+        <v>-0.11556918503942692</v>
       </c>
       <c r="L37" s="0">
-        <v>0.096997475125250976</v>
+        <v>0.0016075111992680524</v>
       </c>
       <c r="M37" s="0">
-        <v>0.27994862953067101</v>
+        <v>-0.091365391387016048</v>
       </c>
       <c r="N37" s="0">
         <v>1</v>
@@ -1752,40 +1752,40 @@
         <v>4920</v>
       </c>
       <c r="B38" s="0">
-        <v>1.4593856828865901e-08</v>
+        <v>1.41201531489028e-08</v>
       </c>
       <c r="C38" s="0">
-        <v>0.25256069189702102</v>
+        <v>0.75008658534154204</v>
       </c>
       <c r="D38" s="0">
-        <v>18.875149951475802</v>
+        <v>18.8827761224466</v>
       </c>
       <c r="E38" s="0">
-        <v>-24.965</v>
+        <v>2.3076808383504e-07</v>
       </c>
       <c r="F38" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75000213515402503</v>
       </c>
       <c r="G38" s="0">
-        <v>37.108333333333299</v>
+        <v>17.3342526674836</v>
       </c>
       <c r="H38" s="0">
-        <v>-0.24455113207891399</v>
+        <v>9.3754083165875903e-07</v>
       </c>
       <c r="I38" s="0">
-        <v>-214.12906752292</v>
+        <v>0.85025068499525303</v>
       </c>
       <c r="J38" s="0">
-        <v>121.357744015259</v>
+        <v>22.637130903594301</v>
       </c>
       <c r="K38" s="0">
-        <v>-0.25256067730316417</v>
+        <v>-0.75008657122138889</v>
       </c>
       <c r="L38" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.75000190438594116</v>
       </c>
       <c r="M38" s="0">
-        <v>213.88451639084107</v>
+        <v>-0.85024974745442139</v>
       </c>
       <c r="N38" s="0">
         <v>0</v>
@@ -1796,40 +1796,40 @@
         <v>4961</v>
       </c>
       <c r="B39" s="0">
-        <v>1.3883927632484999e-08</v>
+        <v>7.0997126526853399e-08</v>
       </c>
       <c r="C39" s="0">
-        <v>0.25853861667615402</v>
+        <v>0.73963597635812905</v>
       </c>
       <c r="D39" s="0">
-        <v>2.0076029255281802</v>
+        <v>2.0076034369873099</v>
       </c>
       <c r="E39" s="0">
-        <v>-0.173171548186315</v>
+        <v>2.1171675153758599e-07</v>
       </c>
       <c r="F39" s="0">
-        <v>-0.70932847731406001</v>
+        <v>0.75318887554582004</v>
       </c>
       <c r="G39" s="0">
-        <v>1.7618412626001501</v>
+        <v>2.0076020741938301</v>
       </c>
       <c r="H39" s="0">
-        <v>-0.058935532263219403</v>
+        <v>2.9505692562114298e-07</v>
       </c>
       <c r="I39" s="0">
-        <v>-0.65196508678252596</v>
+        <v>0.76606538540998903</v>
       </c>
       <c r="J39" s="0">
-        <v>1.7736853600715301</v>
+        <v>2.0076041746056399</v>
       </c>
       <c r="K39" s="0">
-        <v>-0.2585386027922264</v>
+        <v>-0.73963590536100254</v>
       </c>
       <c r="L39" s="0">
-        <v>0.53615692912774504</v>
+        <v>-0.75318866382906846</v>
       </c>
       <c r="M39" s="0">
-        <v>0.5930295545193065</v>
+        <v>-0.76606509035306336</v>
       </c>
       <c r="N39" s="0">
         <v>1</v>
@@ -1840,40 +1840,40 @@
         <v>5096</v>
       </c>
       <c r="B40" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C40" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D40" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E40" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F40" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G40" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H40" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I40" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J40" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K40" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L40" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M40" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N40" s="0">
         <v>1</v>
@@ -1884,40 +1884,40 @@
         <v>5113</v>
       </c>
       <c r="B41" s="0">
-        <v>0.49999999484403701</v>
+        <v>1.4999994580488001</v>
       </c>
       <c r="C41" s="0">
-        <v>0.21513917379452699</v>
+        <v>0.68078192183813302</v>
       </c>
       <c r="D41" s="0">
-        <v>1.88824394017661</v>
+        <v>3.6602701104441802</v>
       </c>
       <c r="E41" s="0">
-        <v>2.0000000002661502</v>
+        <v>1.4999995199610101</v>
       </c>
       <c r="F41" s="0">
-        <v>4.41807610932418</v>
+        <v>0.92141770999747197</v>
       </c>
       <c r="G41" s="0">
-        <v>36.945558664039098</v>
+        <v>3.7985162187569799</v>
       </c>
       <c r="H41" s="0">
-        <v>1.99999999971391</v>
+        <v>1.4999999168407201</v>
       </c>
       <c r="I41" s="0">
-        <v>-60.487436804044798</v>
+        <v>0.66140035155023602</v>
       </c>
       <c r="J41" s="0">
-        <v>114.957523325571</v>
+        <v>9.1673656381956299</v>
       </c>
       <c r="K41" s="0">
-        <v>0.28486082104951005</v>
+        <v>0.81921753621066706</v>
       </c>
       <c r="L41" s="0">
-        <v>-2.4180761090580298</v>
+        <v>0.57858180996353814</v>
       </c>
       <c r="M41" s="0">
-        <v>62.487436803758705</v>
+        <v>0.83859956529048407</v>
       </c>
       <c r="N41" s="0">
         <v>0</v>
@@ -1928,40 +1928,40 @@
         <v>5156</v>
       </c>
       <c r="B42" s="0">
-        <v>0.00065886594430574603</v>
+        <v>0.00065874846259499499</v>
       </c>
       <c r="C42" s="0">
-        <v>0.249744288632259</v>
+        <v>0.73643406294253799</v>
       </c>
       <c r="D42" s="0">
-        <v>2.1973261593236302</v>
+        <v>2.19732566181596</v>
       </c>
       <c r="E42" s="0">
-        <v>-0.040857701650013803</v>
+        <v>1.50644183583849e-07</v>
       </c>
       <c r="F42" s="0">
-        <v>-1.0849599778504999</v>
+        <v>0.74173111650732004</v>
       </c>
       <c r="G42" s="0">
-        <v>2.1098539172174902</v>
+        <v>2.19282426438506</v>
       </c>
       <c r="H42" s="0">
-        <v>0.0040625406626174599</v>
+        <v>0.0040635493488721504</v>
       </c>
       <c r="I42" s="0">
-        <v>-1.5774627626156501</v>
+        <v>0.717888259239857</v>
       </c>
       <c r="J42" s="0">
-        <v>2.2134376161511899</v>
+        <v>2.2134131032059301</v>
       </c>
       <c r="K42" s="0">
-        <v>-0.24908542268795325</v>
+        <v>-0.73577531447994304</v>
       </c>
       <c r="L42" s="0">
-        <v>1.0441022762004861</v>
+        <v>-0.74173096586313647</v>
       </c>
       <c r="M42" s="0">
-        <v>1.5815253032782675</v>
+        <v>-0.7138247098909849</v>
       </c>
       <c r="N42" s="0">
         <v>0</v>
@@ -1972,40 +1972,40 @@
         <v>5273</v>
       </c>
       <c r="B43" s="0">
-        <v>2.1924229993415699e-09</v>
+        <v>2.1923921629314398e-09</v>
       </c>
       <c r="C43" s="0">
-        <v>0.252196944751295</v>
+        <v>0.74457310132375598</v>
       </c>
       <c r="D43" s="0">
-        <v>2.1815823797786398</v>
+        <v>2.1815823425549099</v>
       </c>
       <c r="E43" s="0">
-        <v>-0.20408300534295601</v>
+        <v>1.4686666124985201e-07</v>
       </c>
       <c r="F43" s="0">
-        <v>-0.30869412729456902</v>
+        <v>0.74185080786776503</v>
       </c>
       <c r="G43" s="0">
-        <v>1.89534212443462</v>
+        <v>2.1815827145594202</v>
       </c>
       <c r="H43" s="0">
-        <v>-0.053255886896813598</v>
+        <v>1.9513352398455999e-07</v>
       </c>
       <c r="I43" s="0">
-        <v>-1.8114099261377099</v>
+        <v>0.74350142541931996</v>
       </c>
       <c r="J43" s="0">
-        <v>1.97522645895351</v>
+        <v>2.1815832435782299</v>
       </c>
       <c r="K43" s="0">
-        <v>-0.25219694255887198</v>
+        <v>-0.74457309913136382</v>
       </c>
       <c r="L43" s="0">
-        <v>0.10461112195161301</v>
+        <v>-0.74185066100110375</v>
       </c>
       <c r="M43" s="0">
-        <v>1.7581540392408963</v>
+        <v>-0.74350123028579596</v>
       </c>
       <c r="N43" s="0">
         <v>1</v>
@@ -2016,40 +2016,40 @@
         <v>5495</v>
       </c>
       <c r="B44" s="0">
-        <v>0.062816779811488296</v>
+        <v>0.062816791082920903</v>
       </c>
       <c r="C44" s="0">
-        <v>0.250044722525741</v>
+        <v>0.74856701827027605</v>
       </c>
       <c r="D44" s="0">
-        <v>1.27583533696715</v>
+        <v>1.27583538939033</v>
       </c>
       <c r="E44" s="0">
-        <v>0.24360365592255401</v>
+        <v>0.24360546050812601</v>
       </c>
       <c r="F44" s="0">
-        <v>0.43653437916870103</v>
+        <v>0.75219254934450896</v>
       </c>
       <c r="G44" s="0">
-        <v>1.35453354430766</v>
+        <v>1.3545046742843601</v>
       </c>
       <c r="H44" s="0">
-        <v>0.32403275292755201</v>
+        <v>0.32404184679391501</v>
       </c>
       <c r="I44" s="0">
-        <v>0.83452968936519401</v>
+        <v>0.77976324718018997</v>
       </c>
       <c r="J44" s="0">
-        <v>1.90615615925478</v>
+        <v>1.90618210844761</v>
       </c>
       <c r="K44" s="0">
-        <v>-0.18722794271425269</v>
+        <v>-0.68575022718735512</v>
       </c>
       <c r="L44" s="0">
-        <v>-0.19293072324614702</v>
+        <v>-0.50858708883638293</v>
       </c>
       <c r="M44" s="0">
-        <v>-0.51049693643764193</v>
+        <v>-0.45572140038627496</v>
       </c>
       <c r="N44" s="0">
         <v>0</v>
@@ -2060,40 +2060,40 @@
         <v>5654</v>
       </c>
       <c r="B45" s="0">
-        <v>0.23347139232241301</v>
+        <v>0.23347139210242099</v>
       </c>
       <c r="C45" s="0">
-        <v>0.24979741815564899</v>
+        <v>0.70096649006096901</v>
       </c>
       <c r="D45" s="0">
-        <v>1.3255619439903701</v>
+        <v>1.3255619639726699</v>
       </c>
       <c r="E45" s="0">
-        <v>0.68756061928488599</v>
+        <v>0.687563415128563</v>
       </c>
       <c r="F45" s="0">
-        <v>-0.50930904852803305</v>
+        <v>0.75459806945653896</v>
       </c>
       <c r="G45" s="0">
-        <v>1.5448337558112499</v>
+        <v>1.5448316549798999</v>
       </c>
       <c r="H45" s="0">
-        <v>0.84124010722587805</v>
+        <v>0.84123816816752395</v>
       </c>
       <c r="I45" s="0">
-        <v>-0.971756242104174</v>
+        <v>0.77898790845699495</v>
       </c>
       <c r="J45" s="0">
-        <v>3.0273050083522901</v>
+        <v>3.0272875457922499</v>
       </c>
       <c r="K45" s="0">
-        <v>-0.016326025833235974</v>
+        <v>-0.46749509795854804</v>
       </c>
       <c r="L45" s="0">
-        <v>1.1968696678129191</v>
+        <v>-0.067034654327975951</v>
       </c>
       <c r="M45" s="0">
-        <v>1.812996349330052</v>
+        <v>0.062250259710528999</v>
       </c>
       <c r="N45" s="0">
         <v>0</v>
@@ -2104,40 +2104,40 @@
         <v>5822</v>
       </c>
       <c r="B46" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C46" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D46" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E46" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F46" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G46" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H46" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I46" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J46" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K46" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L46" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M46" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N46" s="0">
         <v>1</v>
@@ -2148,40 +2148,40 @@
         <v>5835</v>
       </c>
       <c r="B47" s="0">
-        <v>2.55104670247109e-09</v>
+        <v>1.5703105701881801e-06</v>
       </c>
       <c r="C47" s="0">
-        <v>0.13910098625464201</v>
+        <v>0.75008318953489705</v>
       </c>
       <c r="D47" s="0">
-        <v>20.901813460934601</v>
+        <v>16.952900810569801</v>
       </c>
       <c r="E47" s="0">
-        <v>-0.0048428917226100996</v>
+        <v>2.8767867930187203e-07</v>
       </c>
       <c r="F47" s="0">
-        <v>-0.56824283001869302</v>
+        <v>0.75001421822918002</v>
       </c>
       <c r="G47" s="0">
-        <v>29.3160181808766</v>
+        <v>18.536323705171402</v>
       </c>
       <c r="H47" s="0">
-        <v>-0.00019853257000296799</v>
+        <v>5.8869699401711599e-08</v>
       </c>
       <c r="I47" s="0">
-        <v>-683.60970260258796</v>
+        <v>0.29222811361011902</v>
       </c>
       <c r="J47" s="0">
-        <v>710.00019576748298</v>
+        <v>18.1210834032062</v>
       </c>
       <c r="K47" s="0">
-        <v>-0.1391009837035953</v>
+        <v>-0.75008161922432681</v>
       </c>
       <c r="L47" s="0">
-        <v>0.56339993829608292</v>
+        <v>-0.7500139305505007</v>
       </c>
       <c r="M47" s="0">
-        <v>683.60950407001792</v>
+        <v>-0.29222805474041963</v>
       </c>
       <c r="N47" s="0">
         <v>1</v>
@@ -2192,40 +2192,40 @@
         <v>5918</v>
       </c>
       <c r="B48" s="0">
-        <v>0.499999616729845</v>
+        <v>0.80493368223160899</v>
       </c>
       <c r="C48" s="0">
-        <v>0.25080458032009301</v>
+        <v>0.69409761271308501</v>
       </c>
       <c r="D48" s="0">
-        <v>0.91206842942787902</v>
+        <v>0.752325521418438</v>
       </c>
       <c r="E48" s="0">
-        <v>1.57541351042808</v>
+        <v>1.4999996485944</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.0009082093094801</v>
+        <v>0.74990497705140702</v>
       </c>
       <c r="G48" s="0">
-        <v>0.785602491659524</v>
+        <v>0.817525920103362</v>
       </c>
       <c r="H48" s="0">
-        <v>2.7936760026051202</v>
+        <v>1.4999993272579799</v>
       </c>
       <c r="I48" s="0">
-        <v>-3.3014208401721601</v>
+        <v>0.75182536121181498</v>
       </c>
       <c r="J48" s="0">
-        <v>1.1560462251291099</v>
+        <v>1.2129607595590399</v>
       </c>
       <c r="K48" s="0">
-        <v>0.24919503640975199</v>
+        <v>0.11083606951852398</v>
       </c>
       <c r="L48" s="0">
-        <v>2.5763217197375603</v>
+        <v>0.75009467154299303</v>
       </c>
       <c r="M48" s="0">
-        <v>6.0950968427772807</v>
+        <v>0.74817396604616493</v>
       </c>
       <c r="N48" s="0">
         <v>0</v>
@@ -2236,40 +2236,40 @@
         <v>6055</v>
       </c>
       <c r="B49" s="0">
-        <v>4.5661683137799102e-08</v>
+        <v>9.1331078349163006e-09</v>
       </c>
       <c r="C49" s="0">
-        <v>0.25114724414165601</v>
+        <v>0.70855139566994796</v>
       </c>
       <c r="D49" s="0">
-        <v>1.58740111959999</v>
+        <v>1.58740104587069</v>
       </c>
       <c r="E49" s="0">
-        <v>-0.39769634689118999</v>
+        <v>1.5369567424718299e-07</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.48922523514572502</v>
+        <v>0.65439405321904598</v>
       </c>
       <c r="G49" s="0">
-        <v>1.2682830671549099</v>
+        <v>1.5874010410073001</v>
       </c>
       <c r="H49" s="0">
-        <v>-0.079610924009866704</v>
+        <v>2.4241241155288098e-07</v>
       </c>
       <c r="I49" s="0">
-        <v>-0.75350556591469897</v>
+        <v>0.63102310684166296</v>
       </c>
       <c r="J49" s="0">
-        <v>1.34523391499788</v>
+        <v>1.5874013751807401</v>
       </c>
       <c r="K49" s="0">
-        <v>-0.25114719847997286</v>
+        <v>-0.70855138653684013</v>
       </c>
       <c r="L49" s="0">
-        <v>0.091528888254535035</v>
+        <v>-0.65439389952337168</v>
       </c>
       <c r="M49" s="0">
-        <v>0.67389464190483228</v>
+        <v>-0.63102286442925137</v>
       </c>
       <c r="N49" s="0">
         <v>0</v>
@@ -2280,40 +2280,40 @@
         <v>6121</v>
       </c>
       <c r="B50" s="0">
-        <v>1.7436398607017301e-10</v>
+        <v>1.41967979653206e-08</v>
       </c>
       <c r="C50" s="0">
-        <v>0.418786867086828</v>
+        <v>0.74981860910365805</v>
       </c>
       <c r="D50" s="0">
-        <v>15.2613445413979</v>
+        <v>18.798628304133999</v>
       </c>
       <c r="E50" s="0">
-        <v>-24.965</v>
+        <v>4.2340172195802302e-08</v>
       </c>
       <c r="F50" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.887974158783564</v>
       </c>
       <c r="G50" s="0">
-        <v>37.108333333333299</v>
+        <v>18.890351819190599</v>
       </c>
       <c r="H50" s="0">
-        <v>-0.22857891151241</v>
+        <v>5.1956518724761503e-08</v>
       </c>
       <c r="I50" s="0">
-        <v>-279.209154384496</v>
+        <v>1.28714309875236</v>
       </c>
       <c r="J50" s="0">
-        <v>158.13435605280799</v>
+        <v>15.364054731767499</v>
       </c>
       <c r="K50" s="0">
-        <v>-0.41878686691246403</v>
+        <v>-0.74981859490686009</v>
       </c>
       <c r="L50" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.88797411644339186</v>
       </c>
       <c r="M50" s="0">
-        <v>278.98057547298362</v>
+        <v>-1.2871430467958414</v>
       </c>
       <c r="N50" s="0">
         <v>0</v>
@@ -2324,40 +2324,40 @@
         <v>6246</v>
       </c>
       <c r="B51" s="0">
-        <v>0.49999988544325202</v>
+        <v>0.67033021327532405</v>
       </c>
       <c r="C51" s="0">
-        <v>0.25043253032064999</v>
+        <v>0.69346076306607796</v>
       </c>
       <c r="D51" s="0">
-        <v>0.91206846130346797</v>
+        <v>0.79803315134617503</v>
       </c>
       <c r="E51" s="0">
-        <v>1.5664102485337399</v>
+        <v>1.4999999457300801</v>
       </c>
       <c r="F51" s="0">
-        <v>-1.68820745485065</v>
+        <v>0.75112645710563497</v>
       </c>
       <c r="G51" s="0">
-        <v>1.1344961309385999</v>
+        <v>1.1683103160057</v>
       </c>
       <c r="H51" s="0">
-        <v>5.5240718517880403</v>
+        <v>1.4999999945714</v>
       </c>
       <c r="I51" s="0">
-        <v>-5.9219631857968702</v>
+        <v>1.14810669666384</v>
       </c>
       <c r="J51" s="0">
-        <v>3.2063665824905399</v>
+        <v>3.8851633233701799</v>
       </c>
       <c r="K51" s="0">
-        <v>0.24956735512260203</v>
+        <v>-0.023130549790753907</v>
       </c>
       <c r="L51" s="0">
-        <v>3.2546177033843899</v>
+        <v>0.74887348862444514</v>
       </c>
       <c r="M51" s="0">
-        <v>11.44603503758491</v>
+        <v>0.35189329790755997</v>
       </c>
       <c r="N51" s="0">
         <v>1</v>
@@ -2368,40 +2368,40 @@
         <v>6324</v>
       </c>
       <c r="B52" s="0">
-        <v>0.111422818839905</v>
+        <v>0.11142282272826</v>
       </c>
       <c r="C52" s="0">
-        <v>0.25005395406703501</v>
+        <v>0.74998653131275395</v>
       </c>
       <c r="D52" s="0">
-        <v>1.2796223047851201</v>
+        <v>1.2796222755023099</v>
       </c>
       <c r="E52" s="0">
-        <v>0.41660300694575803</v>
+        <v>0.416590494599691</v>
       </c>
       <c r="F52" s="0">
-        <v>-0.50492029490622203</v>
+        <v>0.73483392930468605</v>
       </c>
       <c r="G52" s="0">
-        <v>1.4269756851733899</v>
+        <v>1.4269433060196299</v>
       </c>
       <c r="H52" s="0">
-        <v>0.55554845002806097</v>
+        <v>0.55554381777501805</v>
       </c>
       <c r="I52" s="0">
-        <v>-0.93964462655774506</v>
+        <v>0.79324665538176597</v>
       </c>
       <c r="J52" s="0">
-        <v>2.4306108478272899</v>
+        <v>2.4305910808469098</v>
       </c>
       <c r="K52" s="0">
-        <v>-0.13863113522713</v>
+        <v>-0.63856370858449396</v>
       </c>
       <c r="L52" s="0">
-        <v>0.92152330185198006</v>
+        <v>-0.31824343470499505</v>
       </c>
       <c r="M52" s="0">
-        <v>1.4951930765858061</v>
+        <v>-0.23770283760674793</v>
       </c>
       <c r="N52" s="0">
         <v>1</v>
@@ -2412,40 +2412,40 @@
         <v>6332</v>
       </c>
       <c r="B53" s="0">
-        <v>0.27749867866904498</v>
+        <v>0.27749868325399302</v>
       </c>
       <c r="C53" s="0">
-        <v>0.24688294417830201</v>
+        <v>0.74701002871808897</v>
       </c>
       <c r="D53" s="0">
-        <v>0.47075230728738998</v>
+        <v>0.47075232853201199</v>
       </c>
       <c r="E53" s="0">
-        <v>0.96196176835065195</v>
+        <v>0.96197662575696996</v>
       </c>
       <c r="F53" s="0">
-        <v>-0.68343016468571405</v>
+        <v>0.75282394742595204</v>
       </c>
       <c r="G53" s="0">
-        <v>0.67487863276476301</v>
+        <v>0.67486622335903601</v>
       </c>
       <c r="H53" s="0">
-        <v>144.00013103381701</v>
+        <v>1.49999998940753</v>
       </c>
       <c r="I53" s="0">
-        <v>-67.985220203165497</v>
+        <v>0.76835256407672003</v>
       </c>
       <c r="J53" s="0">
-        <v>1.77001360677042</v>
+        <v>2.16520169165232</v>
       </c>
       <c r="K53" s="0">
-        <v>0.03061573449074298</v>
+        <v>-0.46951134546409595</v>
       </c>
       <c r="L53" s="0">
-        <v>1.645391933036366</v>
+        <v>0.20915267833101792</v>
       </c>
       <c r="M53" s="0">
-        <v>211.98535123698252</v>
+        <v>0.73164742533080995</v>
       </c>
       <c r="N53" s="0">
         <v>1</v>
@@ -2456,40 +2456,40 @@
         <v>6335</v>
       </c>
       <c r="B54" s="0">
-        <v>6.5712161790289399e-09</v>
+        <v>6.5712196451856999e-09</v>
       </c>
       <c r="C54" s="0">
-        <v>0.25125204448935401</v>
+        <v>0.72925433013010998</v>
       </c>
       <c r="D54" s="0">
-        <v>2.1928248190375101</v>
+        <v>2.1928236191784198</v>
       </c>
       <c r="E54" s="0">
-        <v>-0.41167468703279098</v>
+        <v>9.8559388999504894e-08</v>
       </c>
       <c r="F54" s="0">
-        <v>-0.43287507244683998</v>
+        <v>0.73888079570849097</v>
       </c>
       <c r="G54" s="0">
-        <v>1.77031851483276</v>
+        <v>2.1928240035670901</v>
       </c>
       <c r="H54" s="0">
-        <v>-0.080295736990482799</v>
+        <v>3.1703112789170001e-08</v>
       </c>
       <c r="I54" s="0">
-        <v>-0.16734924327504599</v>
+        <v>0.74329584687681605</v>
       </c>
       <c r="J54" s="0">
-        <v>1.88448459539195</v>
+        <v>2.1928237695956398</v>
       </c>
       <c r="K54" s="0">
-        <v>-0.25125203791813783</v>
+        <v>-0.72925432355889031</v>
       </c>
       <c r="L54" s="0">
-        <v>0.021200385414049006</v>
+        <v>-0.73888069714910198</v>
       </c>
       <c r="M54" s="0">
-        <v>0.087053506284563195</v>
+        <v>-0.74329581517370324</v>
       </c>
       <c r="N54" s="0">
         <v>0</v>
@@ -2500,40 +2500,40 @@
         <v>6397</v>
       </c>
       <c r="B55" s="0">
-        <v>1.41739368191465e-08</v>
+        <v>1.41149552700507e-08</v>
       </c>
       <c r="C55" s="0">
-        <v>0.24998744256379399</v>
+        <v>0.75003614405224495</v>
       </c>
       <c r="D55" s="0">
-        <v>18.775772519524299</v>
+        <v>18.889711168296401</v>
       </c>
       <c r="E55" s="0">
-        <v>-24.965</v>
+        <v>4.2510970030221202e-08</v>
       </c>
       <c r="F55" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.74998764926750505</v>
       </c>
       <c r="G55" s="0">
-        <v>37.108333333333299</v>
+        <v>18.808586689695399</v>
       </c>
       <c r="H55" s="0">
-        <v>-0.24455113207891399</v>
+        <v>4.24390792960197e-08</v>
       </c>
       <c r="I55" s="0">
-        <v>-214.12906752292</v>
+        <v>0.74999998863444095</v>
       </c>
       <c r="J55" s="0">
-        <v>121.357744015259</v>
+        <v>18.8510052383789</v>
       </c>
       <c r="K55" s="0">
-        <v>-0.24998742838985716</v>
+        <v>-0.75003612993728963</v>
       </c>
       <c r="L55" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.74998760675653497</v>
       </c>
       <c r="M55" s="0">
-        <v>213.88451639084107</v>
+        <v>-0.7499999461953617</v>
       </c>
       <c r="N55" s="0">
         <v>0</v>
@@ -2544,40 +2544,40 @@
         <v>6469</v>
       </c>
       <c r="B56" s="0">
-        <v>0.047351838266211102</v>
+        <v>0.047351838881656103</v>
       </c>
       <c r="C56" s="0">
-        <v>0.25052163551846701</v>
+        <v>0.75538372358657302</v>
       </c>
       <c r="D56" s="0">
-        <v>1.5747599416931299</v>
+        <v>1.57475992232188</v>
       </c>
       <c r="E56" s="0">
-        <v>0.100096669051536</v>
+        <v>0.100086152831623</v>
       </c>
       <c r="F56" s="0">
-        <v>-0.38328660212526899</v>
+        <v>0.74531719754944703</v>
       </c>
       <c r="G56" s="0">
-        <v>1.48724040183707</v>
+        <v>1.4872544327841899</v>
       </c>
       <c r="H56" s="0">
-        <v>0.13190347901652899</v>
+        <v>0.131903251197556</v>
       </c>
       <c r="I56" s="0">
-        <v>2.9684974015517298</v>
+        <v>0.770545233235719</v>
       </c>
       <c r="J56" s="0">
-        <v>1.8236349083603201</v>
+        <v>1.8236140430582499</v>
       </c>
       <c r="K56" s="0">
-        <v>-0.20316979725225592</v>
+        <v>-0.70803188470491696</v>
       </c>
       <c r="L56" s="0">
-        <v>0.48338327117680502</v>
+        <v>-0.645231044717824</v>
       </c>
       <c r="M56" s="0">
-        <v>-2.8365939225352008</v>
+        <v>-0.63864198203816303</v>
       </c>
       <c r="N56" s="0">
         <v>1</v>
@@ -2588,40 +2588,40 @@
         <v>6495</v>
       </c>
       <c r="B57" s="0">
-        <v>1.3731312575772e-07</v>
+        <v>1.3731320601088801e-07</v>
       </c>
       <c r="C57" s="0">
-        <v>0.25041866286487402</v>
+        <v>0.69586069763862202</v>
       </c>
       <c r="D57" s="0">
-        <v>1.8042301680033499</v>
+        <v>1.80423026091196</v>
       </c>
       <c r="E57" s="0">
-        <v>-0.069285949627791596</v>
+        <v>1.01225471350442e-07</v>
       </c>
       <c r="F57" s="0">
-        <v>-0.246026481164552</v>
+        <v>0.68388894251642096</v>
       </c>
       <c r="G57" s="0">
-        <v>1.7025156539667701</v>
+        <v>1.80422968756264</v>
       </c>
       <c r="H57" s="0">
-        <v>0.028724151668438599</v>
+        <v>0.028720793125492299</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.81058210003652797</v>
+        <v>0.72229991776816505</v>
       </c>
       <c r="J57" s="0">
-        <v>1.9225932242199499</v>
+        <v>1.9225942810266501</v>
       </c>
       <c r="K57" s="0">
-        <v>-0.25041852555174826</v>
+        <v>-0.69586056032541599</v>
       </c>
       <c r="L57" s="0">
-        <v>0.17674053153676039</v>
+        <v>-0.68388884129094962</v>
       </c>
       <c r="M57" s="0">
-        <v>0.83930625170496653</v>
+        <v>-0.6935791246426728</v>
       </c>
       <c r="N57" s="0">
         <v>0</v>
@@ -2632,40 +2632,40 @@
         <v>6604</v>
       </c>
       <c r="B58" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C58" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D58" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E58" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F58" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G58" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H58" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I58" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J58" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K58" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L58" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M58" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N58" s="0">
         <v>0</v>
@@ -2676,40 +2676,40 @@
         <v>6644</v>
       </c>
       <c r="B59" s="0">
-        <v>0.022272435042664698</v>
+        <v>0.022272447249776998</v>
       </c>
       <c r="C59" s="0">
-        <v>0.24754226613128799</v>
+        <v>0.774580847114125</v>
       </c>
       <c r="D59" s="0">
-        <v>0.213064989131104</v>
+        <v>0.21306498299607601</v>
       </c>
       <c r="E59" s="0">
-        <v>0.00060558850825475198</v>
+        <v>0.00068777487782363501</v>
       </c>
       <c r="F59" s="0">
-        <v>0.062291894579093003</v>
+        <v>0.715324402641763</v>
       </c>
       <c r="G59" s="0">
-        <v>0.20240107277573199</v>
+        <v>0.20241485323254299</v>
       </c>
       <c r="H59" s="0">
-        <v>-0.026657154842520101</v>
+        <v>1.98509372212514e-06</v>
       </c>
       <c r="I59" s="0">
-        <v>-0.0140795586084277</v>
+        <v>0.74998964394761203</v>
       </c>
       <c r="J59" s="0">
-        <v>0.19142141282921801</v>
+        <v>0.20231074610649399</v>
       </c>
       <c r="K59" s="0">
-        <v>-0.22526983108862331</v>
+        <v>-0.75230839986434805</v>
       </c>
       <c r="L59" s="0">
-        <v>-0.061686306070838248</v>
+        <v>-0.71463662776393932</v>
       </c>
       <c r="M59" s="0">
-        <v>-0.012577596234092402</v>
+        <v>-0.74998765885388985</v>
       </c>
       <c r="N59" s="0">
         <v>0</v>
@@ -2720,40 +2720,40 @@
         <v>6707</v>
       </c>
       <c r="B60" s="0">
-        <v>1.86848480969332e-10</v>
+        <v>1.8246504095337001e-08</v>
       </c>
       <c r="C60" s="0">
-        <v>0.42029594553209698</v>
+        <v>0.68367731563506795</v>
       </c>
       <c r="D60" s="0">
-        <v>15.2591278309262</v>
+        <v>19.789943389498301</v>
       </c>
       <c r="E60" s="0">
-        <v>-24.965</v>
+        <v>4.6949608973222798e-08</v>
       </c>
       <c r="F60" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75002417069687</v>
       </c>
       <c r="G60" s="0">
-        <v>37.108333333333299</v>
+        <v>18.888182670893599</v>
       </c>
       <c r="H60" s="0">
-        <v>-0.19545403511568099</v>
+        <v>1.87241705533176e-07</v>
       </c>
       <c r="I60" s="0">
-        <v>-291.74500933229598</v>
+        <v>0.97522913156153501</v>
       </c>
       <c r="J60" s="0">
-        <v>165.09901953444501</v>
+        <v>27.710842839678801</v>
       </c>
       <c r="K60" s="0">
-        <v>-0.4202959453452485</v>
+        <v>-0.68367729738856386</v>
       </c>
       <c r="L60" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.75002412374726102</v>
       </c>
       <c r="M60" s="0">
-        <v>291.54955529718029</v>
+        <v>-0.97522894431982943</v>
       </c>
       <c r="N60" s="0">
         <v>1</v>
@@ -2764,40 +2764,40 @@
         <v>7047</v>
       </c>
       <c r="B61" s="0">
-        <v>4.0184280434542301e-07</v>
+        <v>1.11358390667128e-07</v>
       </c>
       <c r="C61" s="0">
-        <v>0.30788381411384702</v>
+        <v>0.74998640352046397</v>
       </c>
       <c r="D61" s="0">
-        <v>19.429854952625298</v>
+        <v>17.104912966511801</v>
       </c>
       <c r="E61" s="0">
-        <v>-24.965</v>
+        <v>6.1523382621968296e-08</v>
       </c>
       <c r="F61" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.76159401336976096</v>
       </c>
       <c r="G61" s="0">
-        <v>37.108333333333299</v>
+        <v>18.5717694082152</v>
       </c>
       <c r="H61" s="0">
-        <v>-0.234925425378054</v>
+        <v>2.0996746849113299e-07</v>
       </c>
       <c r="I61" s="0">
-        <v>-233.57995393932899</v>
+        <v>0.94044824727662102</v>
       </c>
       <c r="J61" s="0">
-        <v>132.31774306443799</v>
+        <v>30.627460325432299</v>
       </c>
       <c r="K61" s="0">
-        <v>-0.30788341227104266</v>
+        <v>-0.74998629216207335</v>
       </c>
       <c r="L61" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.76159395184637835</v>
       </c>
       <c r="M61" s="0">
-        <v>233.34502851395092</v>
+        <v>-0.9404480373091525</v>
       </c>
       <c r="N61" s="0">
         <v>1</v>
@@ -2808,40 +2808,40 @@
         <v>7107</v>
       </c>
       <c r="B62" s="0">
-        <v>2.6740882687472702e-07</v>
+        <v>4.9034607737004703e-08</v>
       </c>
       <c r="C62" s="0">
-        <v>0.25160860592742501</v>
+        <v>0.69358670499198005</v>
       </c>
       <c r="D62" s="0">
-        <v>1.04804902570128</v>
+        <v>1.0480480122246401</v>
       </c>
       <c r="E62" s="0">
-        <v>-0.015527892881608499</v>
+        <v>1.1421410069498999e-06</v>
       </c>
       <c r="F62" s="0">
-        <v>-0.13687584592101101</v>
+        <v>0.67636000713045097</v>
       </c>
       <c r="G62" s="0">
-        <v>1.0348532383579101</v>
+        <v>1.04804901222934</v>
       </c>
       <c r="H62" s="0">
-        <v>0.157882302720181</v>
+        <v>0.15787659551680999</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.3907171937470801</v>
+        <v>0.73383476049072605</v>
       </c>
       <c r="J62" s="0">
-        <v>1.3840783298075101</v>
+        <v>1.38406974125011</v>
       </c>
       <c r="K62" s="0">
-        <v>-0.25160833851859815</v>
+        <v>-0.69358665595737234</v>
       </c>
       <c r="L62" s="0">
-        <v>0.12134795303940252</v>
+        <v>-0.67635886498944398</v>
       </c>
       <c r="M62" s="0">
-        <v>2.5485994964672614</v>
+        <v>-0.57595816497391605</v>
       </c>
       <c r="N62" s="0">
         <v>1</v>
@@ -2852,40 +2852,40 @@
         <v>7389</v>
       </c>
       <c r="B63" s="0">
-        <v>5.9339022080266701e-09</v>
+        <v>5.9342237000073898e-09</v>
       </c>
       <c r="C63" s="0">
-        <v>0.25397135945107102</v>
+        <v>0.72295359519024005</v>
       </c>
       <c r="D63" s="0">
-        <v>2.77172795140965</v>
+        <v>2.7717278535941001</v>
       </c>
       <c r="E63" s="0">
-        <v>-15.322219692720701</v>
+        <v>8.4731269378366801e-08</v>
       </c>
       <c r="F63" s="0">
-        <v>33.195583595497197</v>
+        <v>0.834619321886645</v>
       </c>
       <c r="G63" s="0">
-        <v>2.19282363464538</v>
+        <v>2.7717279842673301</v>
       </c>
       <c r="H63" s="0">
-        <v>-0.24999998959500799</v>
+        <v>1.5023303247752299e-08</v>
       </c>
       <c r="I63" s="0">
-        <v>-3.44185730824156</v>
+        <v>0.85671851043731595</v>
       </c>
       <c r="J63" s="0">
-        <v>2.5250679669384199</v>
+        <v>2.7717279330561002</v>
       </c>
       <c r="K63" s="0">
-        <v>-0.25397135351716882</v>
+        <v>-0.72295358925601638</v>
       </c>
       <c r="L63" s="0">
-        <v>-48.517803288217898</v>
+        <v>-0.83461923715537567</v>
       </c>
       <c r="M63" s="0">
-        <v>3.191857318646552</v>
+        <v>-0.85671849541401268</v>
       </c>
       <c r="N63" s="0">
         <v>1</v>
@@ -2896,40 +2896,40 @@
         <v>7512</v>
       </c>
       <c r="B64" s="0">
-        <v>7.5626068428279003e-10</v>
+        <v>9.0933417994810406e-08</v>
       </c>
       <c r="C64" s="0">
-        <v>0.25042821010127297</v>
+        <v>0.74999598273385504</v>
       </c>
       <c r="D64" s="0">
-        <v>20.763211211034999</v>
+        <v>17.250717206800399</v>
       </c>
       <c r="E64" s="0">
-        <v>-24.965</v>
+        <v>4.2451061110772299e-10</v>
       </c>
       <c r="F64" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.653560312969933</v>
       </c>
       <c r="G64" s="0">
-        <v>37.108333333333299</v>
+        <v>22.123659476982301</v>
       </c>
       <c r="H64" s="0">
-        <v>-0.248671771390156</v>
+        <v>5.0111797347520999e-08</v>
       </c>
       <c r="I64" s="0">
-        <v>-195.059051746259</v>
+        <v>0.74999229122078603</v>
       </c>
       <c r="J64" s="0">
-        <v>110.63724739046</v>
+        <v>18.7825162806759</v>
       </c>
       <c r="K64" s="0">
-        <v>-0.25042820934501231</v>
+        <v>-0.74999589180043702</v>
       </c>
       <c r="L64" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.65356031254542235</v>
       </c>
       <c r="M64" s="0">
-        <v>194.81037997486885</v>
+        <v>-0.74999224110898866</v>
       </c>
       <c r="N64" s="0">
         <v>1</v>
@@ -2940,40 +2940,40 @@
         <v>7656</v>
       </c>
       <c r="B65" s="0">
-        <v>0.30033126278669597</v>
+        <v>0.30033128322245101</v>
       </c>
       <c r="C65" s="0">
-        <v>0.24982651187220201</v>
+        <v>0.75224335930495201</v>
       </c>
       <c r="D65" s="0">
-        <v>0.96352607628668696</v>
+        <v>0.96352603050489405</v>
       </c>
       <c r="E65" s="0">
-        <v>0.88962788694714301</v>
+        <v>0.88961317555189501</v>
       </c>
       <c r="F65" s="0">
-        <v>-0.36324741576298603</v>
+        <v>0.75003088062321399</v>
       </c>
       <c r="G65" s="0">
-        <v>1.0911773622776799</v>
+        <v>1.0912087738290199</v>
       </c>
       <c r="H65" s="0">
-        <v>2.4949989809587301</v>
+        <v>1.49999997108</v>
       </c>
       <c r="I65" s="0">
-        <v>-1.0961083004600001</v>
+        <v>0.74824735299368805</v>
       </c>
       <c r="J65" s="0">
-        <v>2.1743060267158998</v>
+        <v>2.3818550226108202</v>
       </c>
       <c r="K65" s="0">
-        <v>0.050504750914493968</v>
+        <v>-0.451912076082501</v>
       </c>
       <c r="L65" s="0">
-        <v>1.2528753027101289</v>
+        <v>0.13958229492868102</v>
       </c>
       <c r="M65" s="0">
-        <v>3.5911072814187301</v>
+        <v>0.751752618086312</v>
       </c>
       <c r="N65" s="0">
         <v>0</v>
@@ -2984,40 +2984,40 @@
         <v>7772</v>
       </c>
       <c r="B66" s="0">
-        <v>1.61759052620606e-08</v>
+        <v>1.6180053499151302e-08</v>
       </c>
       <c r="C66" s="0">
-        <v>0.25225345258930398</v>
+        <v>0.67550900474897202</v>
       </c>
       <c r="D66" s="0">
-        <v>1.34621402414943</v>
+        <v>1.3462139255441801</v>
       </c>
       <c r="E66" s="0">
-        <v>-0.25289442927512201</v>
+        <v>2.5259761693550502e-07</v>
       </c>
       <c r="F66" s="0">
-        <v>-0.58594842805313196</v>
+        <v>0.65465775059924902</v>
       </c>
       <c r="G66" s="0">
-        <v>1.13849948648249</v>
+        <v>1.3462143360836201</v>
       </c>
       <c r="H66" s="0">
-        <v>-0.121786691142394</v>
+        <v>7.2540935355011496e-08</v>
       </c>
       <c r="I66" s="0">
-        <v>-0.30000018620251701</v>
+        <v>0.62531533565104902</v>
       </c>
       <c r="J66" s="0">
-        <v>1.06019948930807</v>
+        <v>1.34621398159225</v>
       </c>
       <c r="K66" s="0">
-        <v>-0.2522534364133987</v>
+        <v>-0.6755089885689185</v>
       </c>
       <c r="L66" s="0">
-        <v>0.33305399877800995</v>
+        <v>-0.65465749800163209</v>
       </c>
       <c r="M66" s="0">
-        <v>0.17821349506012302</v>
+        <v>-0.62531526311011365</v>
       </c>
       <c r="N66" s="0">
         <v>0</v>
@@ -3028,40 +3028,40 @@
         <v>7803</v>
       </c>
       <c r="B67" s="0">
-        <v>0.14786362926152799</v>
+        <v>0.14786364135907001</v>
       </c>
       <c r="C67" s="0">
-        <v>0.24819678000214701</v>
+        <v>0.75071767126201305</v>
       </c>
       <c r="D67" s="0">
-        <v>0.30713610098434801</v>
+        <v>0.30713607504537199</v>
       </c>
       <c r="E67" s="0">
-        <v>0.33326673718990002</v>
+        <v>0.33329010534513698</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.088163987174583999</v>
+        <v>0.73940589086836195</v>
       </c>
       <c r="G67" s="0">
-        <v>0.27125855879493699</v>
+        <v>0.27124314458131299</v>
       </c>
       <c r="H67" s="0">
-        <v>0.095568120200171899</v>
+        <v>0.095570128980342603</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.051576798099369402</v>
+        <v>0.74536757109729501</v>
       </c>
       <c r="J67" s="0">
-        <v>0.242923565176244</v>
+        <v>0.24292700155380001</v>
       </c>
       <c r="K67" s="0">
-        <v>-0.10033315074061902</v>
+        <v>-0.60285402990294301</v>
       </c>
       <c r="L67" s="0">
-        <v>0.42143072436448403</v>
+        <v>-0.40611578552322497</v>
       </c>
       <c r="M67" s="0">
-        <v>0.14714491829954129</v>
+        <v>-0.64979744211695245</v>
       </c>
       <c r="N67" s="0">
         <v>0</v>
@@ -3072,40 +3072,40 @@
         <v>7875</v>
       </c>
       <c r="B68" s="0">
-        <v>6.0461477095596301e-10</v>
+        <v>1.68902988545506e-08</v>
       </c>
       <c r="C68" s="0">
-        <v>0.24999986071010999</v>
+        <v>0.75000800956997704</v>
       </c>
       <c r="D68" s="0">
-        <v>26.4632907476594</v>
+        <v>18.951340271564199</v>
       </c>
       <c r="E68" s="0">
-        <v>-24.965</v>
+        <v>5.3009520909755302e-08</v>
       </c>
       <c r="F68" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.75000022653625098</v>
       </c>
       <c r="G68" s="0">
-        <v>37.108333333333299</v>
+        <v>18.8626600355921</v>
       </c>
       <c r="H68" s="0">
-        <v>-0.190979485866837</v>
+        <v>2.8994094455442102e-07</v>
       </c>
       <c r="I68" s="0">
-        <v>-320.92922063252797</v>
+        <v>0.75001679683964595</v>
       </c>
       <c r="J68" s="0">
-        <v>181.619269596511</v>
+        <v>17.243974122718701</v>
       </c>
       <c r="K68" s="0">
-        <v>-0.24999986010549521</v>
+        <v>-0.75000799267967821</v>
       </c>
       <c r="L68" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.7500001735267301</v>
       </c>
       <c r="M68" s="0">
-        <v>320.73824114666115</v>
+        <v>-0.75001650689870136</v>
       </c>
       <c r="N68" s="0">
         <v>1</v>
@@ -3116,40 +3116,40 @@
         <v>7927</v>
       </c>
       <c r="B69" s="0">
-        <v>3.8367835463437603e-09</v>
+        <v>3.7082166940514001e-09</v>
       </c>
       <c r="C69" s="0">
-        <v>0.37412324742490299</v>
+        <v>0.74999999889931401</v>
       </c>
       <c r="D69" s="0">
-        <v>19.026275622256499</v>
+        <v>19.612448591441201</v>
       </c>
       <c r="E69" s="0">
-        <v>-24.965</v>
+        <v>5.2675524669924097e-08</v>
       </c>
       <c r="F69" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.88976497952946498</v>
       </c>
       <c r="G69" s="0">
-        <v>37.108333333333299</v>
+        <v>18.985754846056299</v>
       </c>
       <c r="H69" s="0">
-        <v>-0.21000934093013501</v>
+        <v>5.3238145291653303e-08</v>
       </c>
       <c r="I69" s="0">
-        <v>-254.176340703432</v>
+        <v>0.75013262695205096</v>
       </c>
       <c r="J69" s="0">
-        <v>143.90520323029099</v>
+        <v>18.747268224749099</v>
       </c>
       <c r="K69" s="0">
-        <v>-0.37412324358811944</v>
+        <v>-0.74999999519109728</v>
       </c>
       <c r="L69" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.88976492685394026</v>
       </c>
       <c r="M69" s="0">
-        <v>253.96633136250188</v>
+        <v>-0.75013257371390563</v>
       </c>
       <c r="N69" s="0">
         <v>0</v>
@@ -3160,40 +3160,40 @@
         <v>7937</v>
       </c>
       <c r="B70" s="0">
-        <v>4.4848321980658602e-09</v>
+        <v>4.4846143509401499e-09</v>
       </c>
       <c r="C70" s="0">
-        <v>0.24331443331473601</v>
+        <v>0.75197649703505398</v>
       </c>
       <c r="D70" s="0">
-        <v>2.8259138232150902</v>
+        <v>2.8259148438104398</v>
       </c>
       <c r="E70" s="0">
-        <v>-0.37974114403840498</v>
+        <v>7.70695814333961e-10</v>
       </c>
       <c r="F70" s="0">
-        <v>-1.1859149845829</v>
+        <v>0.83731404708267798</v>
       </c>
       <c r="G70" s="0">
-        <v>2.3354185492438102</v>
+        <v>2.8259148421825802</v>
       </c>
       <c r="H70" s="0">
-        <v>-0.21185622914319199</v>
+        <v>1.4999319650156401e-08</v>
       </c>
       <c r="I70" s="0">
-        <v>-2.7799407013883699</v>
+        <v>0.85575407192653097</v>
       </c>
       <c r="J70" s="0">
-        <v>2.09891978961728</v>
+        <v>2.8259148603772801</v>
       </c>
       <c r="K70" s="0">
-        <v>-0.24331442882990381</v>
+        <v>-0.75197649255043963</v>
       </c>
       <c r="L70" s="0">
-        <v>0.80617384054449504</v>
+        <v>-0.83731404631198214</v>
       </c>
       <c r="M70" s="0">
-        <v>2.5680844722451779</v>
+        <v>-0.85575405692721129</v>
       </c>
       <c r="N70" s="0">
         <v>1</v>
@@ -3204,40 +3204,40 @@
         <v>8228</v>
       </c>
       <c r="B71" s="0">
-        <v>0.112566436301533</v>
+        <v>0.112566441649935</v>
       </c>
       <c r="C71" s="0">
-        <v>0.24891153546774999</v>
+        <v>0.75314430679787803</v>
       </c>
       <c r="D71" s="0">
-        <v>0.66808744544850296</v>
+        <v>0.668087477246602</v>
       </c>
       <c r="E71" s="0">
-        <v>0.43196899067399802</v>
+        <v>0.43197035509225201</v>
       </c>
       <c r="F71" s="0">
-        <v>-0.42204514869987703</v>
+        <v>0.68077716312487602</v>
       </c>
       <c r="G71" s="0">
-        <v>0.75223543711265395</v>
+        <v>0.75224283657886004</v>
       </c>
       <c r="H71" s="0">
-        <v>0.60241366133331797</v>
+        <v>0.60244859775450899</v>
       </c>
       <c r="I71" s="0">
-        <v>-0.408379635945125</v>
+        <v>0.75835509386463296</v>
       </c>
       <c r="J71" s="0">
-        <v>1.22941946733894</v>
+        <v>1.2294213800843301</v>
       </c>
       <c r="K71" s="0">
-        <v>-0.13634509916621701</v>
+        <v>-0.64057786514794302</v>
       </c>
       <c r="L71" s="0">
-        <v>0.85401413937387505</v>
+        <v>-0.24880680803262401</v>
       </c>
       <c r="M71" s="0">
-        <v>1.010793297278443</v>
+        <v>-0.15590649611012397</v>
       </c>
       <c r="N71" s="0">
         <v>1</v>
@@ -3248,40 +3248,40 @@
         <v>8251</v>
       </c>
       <c r="B72" s="0">
-        <v>1.2357004165055101e-08</v>
+        <v>2.47142470353547e-09</v>
       </c>
       <c r="C72" s="0">
-        <v>0.3414495152257</v>
+        <v>0.74557665379852101</v>
       </c>
       <c r="D72" s="0">
-        <v>2.1928295536877802</v>
+        <v>2.19282372990157</v>
       </c>
       <c r="E72" s="0">
-        <v>-0.122561746241235</v>
+        <v>2.14403132773261e-07</v>
       </c>
       <c r="F72" s="0">
-        <v>-0.97015889360941798</v>
+        <v>0.73716239825701702</v>
       </c>
       <c r="G72" s="0">
-        <v>1.98675398213162</v>
+        <v>2.1928241393499999</v>
       </c>
       <c r="H72" s="0">
-        <v>-0.028496729858802899</v>
+        <v>1.0745192476371501e-07</v>
       </c>
       <c r="I72" s="0">
-        <v>-1.7498038173375801</v>
+        <v>0.72459063652140998</v>
       </c>
       <c r="J72" s="0">
-        <v>2.0609972285820501</v>
+        <v>2.1928243573474999</v>
       </c>
       <c r="K72" s="0">
-        <v>-0.34144950286869585</v>
+        <v>-0.74557665132709627</v>
       </c>
       <c r="L72" s="0">
-        <v>0.84759714736818292</v>
+        <v>-0.73716218385388421</v>
       </c>
       <c r="M72" s="0">
-        <v>1.7213070874787773</v>
+        <v>-0.72459052906948518</v>
       </c>
       <c r="N72" s="0">
         <v>1</v>
@@ -3292,40 +3292,40 @@
         <v>8604</v>
       </c>
       <c r="B73" s="0">
-        <v>1.7420516471170099e-10</v>
+        <v>2.6111329066797001e-09</v>
       </c>
       <c r="C73" s="0">
-        <v>0.42927237477190999</v>
+        <v>0.75000000176239201</v>
       </c>
       <c r="D73" s="0">
-        <v>15.275236365121801</v>
+        <v>20.418666478382299</v>
       </c>
       <c r="E73" s="0">
-        <v>-24.965</v>
+        <v>4.2626356337134103e-08</v>
       </c>
       <c r="F73" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.74995735764902105</v>
       </c>
       <c r="G73" s="0">
-        <v>37.108333333333299</v>
+        <v>18.764849574378601</v>
       </c>
       <c r="H73" s="0">
-        <v>-0.22674014629865999</v>
+        <v>3.60881168412449e-10</v>
       </c>
       <c r="I73" s="0">
-        <v>-244.186805025718</v>
+        <v>0.73796013959490203</v>
       </c>
       <c r="J73" s="0">
-        <v>138.30813677601</v>
+        <v>22.1676526046597</v>
       </c>
       <c r="K73" s="0">
-        <v>-0.42927237459770484</v>
+        <v>-0.74999999915125914</v>
       </c>
       <c r="L73" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.74995731502266472</v>
       </c>
       <c r="M73" s="0">
-        <v>243.96006487941935</v>
+        <v>-0.73796013923402082</v>
       </c>
       <c r="N73" s="0">
         <v>1</v>
@@ -3336,40 +3336,40 @@
         <v>8704</v>
       </c>
       <c r="B74" s="0">
-        <v>0.041121122021522398</v>
+        <v>0.041121120382952403</v>
       </c>
       <c r="C74" s="0">
-        <v>0.24986225798426201</v>
+        <v>0.74093103848743402</v>
       </c>
       <c r="D74" s="0">
-        <v>2.09729260282811</v>
+        <v>2.09729257158827</v>
       </c>
       <c r="E74" s="0">
-        <v>0.091361013660355206</v>
+        <v>0.091362073377366501</v>
       </c>
       <c r="F74" s="0">
-        <v>1.0364459969348001</v>
+        <v>0.72898858074909501</v>
       </c>
       <c r="G74" s="0">
-        <v>1.97630504146254</v>
+        <v>1.9762460876082999</v>
       </c>
       <c r="H74" s="0">
-        <v>0.102013031867896</v>
+        <v>0.102013064545164</v>
       </c>
       <c r="I74" s="0">
-        <v>-3.62529243657321</v>
+        <v>0.73455642277944899</v>
       </c>
       <c r="J74" s="0">
-        <v>2.3021747016449199</v>
+        <v>2.3021555073481901</v>
       </c>
       <c r="K74" s="0">
-        <v>-0.2087411359627396</v>
+        <v>-0.69980991810448168</v>
       </c>
       <c r="L74" s="0">
-        <v>-0.9450849832744449</v>
+        <v>-0.63762650737172855</v>
       </c>
       <c r="M74" s="0">
-        <v>3.7273054684411058</v>
+        <v>-0.63254335823428498</v>
       </c>
       <c r="N74" s="0">
         <v>0</v>
@@ -3380,40 +3380,40 @@
         <v>8925</v>
       </c>
       <c r="B75" s="0">
-        <v>0.079114275330828904</v>
+        <v>0.079114290785250202</v>
       </c>
       <c r="C75" s="0">
-        <v>0.25007637881231698</v>
+        <v>0.75003635346445297</v>
       </c>
       <c r="D75" s="0">
-        <v>0.75954441696424901</v>
+        <v>0.75954447622502796</v>
       </c>
       <c r="E75" s="0">
-        <v>0.27006271201954002</v>
+        <v>0.27004874687146002</v>
       </c>
       <c r="F75" s="0">
-        <v>0.321616278466129</v>
+        <v>0.73639662237390602</v>
       </c>
       <c r="G75" s="0">
-        <v>0.78320850535123998</v>
+        <v>0.78318990399649102</v>
       </c>
       <c r="H75" s="0">
-        <v>0.51776467073680699</v>
+        <v>0.51775090623796605</v>
       </c>
       <c r="I75" s="0">
-        <v>-0.44318935557264399</v>
+        <v>0.70671570731945199</v>
       </c>
       <c r="J75" s="0">
-        <v>1.23900586309817</v>
+        <v>1.2390243228164699</v>
       </c>
       <c r="K75" s="0">
-        <v>-0.17096210348148808</v>
+        <v>-0.67092206267920274</v>
       </c>
       <c r="L75" s="0">
-        <v>-0.051553566446588983</v>
+        <v>-0.466347875502446</v>
       </c>
       <c r="M75" s="0">
-        <v>0.96095402630945093</v>
+        <v>-0.18896480108148594</v>
       </c>
       <c r="N75" s="0">
         <v>1</v>
@@ -3424,40 +3424,40 @@
         <v>8949</v>
       </c>
       <c r="B76" s="0">
-        <v>0.048843413549060299</v>
+        <v>0.0488434122840814</v>
       </c>
       <c r="C76" s="0">
-        <v>0.25005897279285</v>
+        <v>0.75009766579192405</v>
       </c>
       <c r="D76" s="0">
-        <v>0.95101928262648605</v>
+        <v>0.95101929657104001</v>
       </c>
       <c r="E76" s="0">
-        <v>0.050123323199618298</v>
+        <v>0.0501228667397512</v>
       </c>
       <c r="F76" s="0">
-        <v>-1.75561751624482</v>
+        <v>0.65256406750185503</v>
       </c>
       <c r="G76" s="0">
-        <v>0.86298451702942403</v>
+        <v>0.86298887791582501</v>
       </c>
       <c r="H76" s="0">
-        <v>0.090691266624100694</v>
+        <v>0.090687004075398106</v>
       </c>
       <c r="I76" s="0">
-        <v>-0.73382741042729105</v>
+        <v>0.74998582078658704</v>
       </c>
       <c r="J76" s="0">
-        <v>1.0001171821518</v>
+        <v>1.0001356877709699</v>
       </c>
       <c r="K76" s="0">
-        <v>-0.2012155592437897</v>
+        <v>-0.70125425350784265</v>
       </c>
       <c r="L76" s="0">
-        <v>1.8057408394444383</v>
+        <v>-0.60244120076210383</v>
       </c>
       <c r="M76" s="0">
-        <v>0.8245186770513917</v>
+        <v>-0.65929881671118895</v>
       </c>
       <c r="N76" s="0">
         <v>0</v>
@@ -3468,40 +3468,40 @@
         <v>8987</v>
       </c>
       <c r="B77" s="0">
-        <v>3.6825723115280898e-09</v>
+        <v>1.76066341392884e-08</v>
       </c>
       <c r="C77" s="0">
-        <v>0.230600815950632</v>
+        <v>0.749992559131614</v>
       </c>
       <c r="D77" s="0">
-        <v>23.2324646315402</v>
+        <v>19.1309797168975</v>
       </c>
       <c r="E77" s="0">
-        <v>-0.013377363387858301</v>
+        <v>8.4557760152526399e-08</v>
       </c>
       <c r="F77" s="0">
-        <v>-0.82142737154350798</v>
+        <v>0.74999633853389502</v>
       </c>
       <c r="G77" s="0">
-        <v>28.234590718633498</v>
+        <v>18.921516233651001</v>
       </c>
       <c r="H77" s="0">
-        <v>-0.0466295947907178</v>
+        <v>8.8905718136376101e-08</v>
       </c>
       <c r="I77" s="0">
-        <v>-12.4491206721616</v>
+        <v>1.13042109315449</v>
       </c>
       <c r="J77" s="0">
-        <v>7.32637935535924</v>
+        <v>17.9919223308321</v>
       </c>
       <c r="K77" s="0">
-        <v>-0.2306008122680597</v>
+        <v>-0.74999254152497985</v>
       </c>
       <c r="L77" s="0">
-        <v>0.80805000815564965</v>
+        <v>-0.7499962539761349</v>
       </c>
       <c r="M77" s="0">
-        <v>12.402491077370883</v>
+        <v>-1.1304210042487719</v>
       </c>
       <c r="N77" s="0">
         <v>0</v>
@@ -3512,40 +3512,40 @@
         <v>9045</v>
       </c>
       <c r="B78" s="0">
-        <v>0.072076798315565002</v>
+        <v>0.072076796624604395</v>
       </c>
       <c r="C78" s="0">
-        <v>0.25064692338658501</v>
+        <v>0.74963588274031701</v>
       </c>
       <c r="D78" s="0">
-        <v>2.9029287671447301</v>
+        <v>2.9029288589363098</v>
       </c>
       <c r="E78" s="0">
-        <v>0.26322223088136498</v>
+        <v>0.26322091105534301</v>
       </c>
       <c r="F78" s="0">
-        <v>-1.3635226544501899</v>
+        <v>0.76540038875472605</v>
       </c>
       <c r="G78" s="0">
-        <v>3.1517035415514498</v>
+        <v>3.1516665618997899</v>
       </c>
       <c r="H78" s="0">
-        <v>0.25631077694135701</v>
+        <v>0.25631105742316002</v>
       </c>
       <c r="I78" s="0">
-        <v>-7.1439574808414203</v>
+        <v>0.75549196893998105</v>
       </c>
       <c r="J78" s="0">
-        <v>4.2635417223329304</v>
+        <v>4.2635359286253598</v>
       </c>
       <c r="K78" s="0">
-        <v>-0.17857012507101999</v>
+        <v>-0.67755908611571258</v>
       </c>
       <c r="L78" s="0">
-        <v>1.6267448853315549</v>
+        <v>-0.50217947769938309</v>
       </c>
       <c r="M78" s="0">
-        <v>7.400268257782777</v>
+        <v>-0.49918091151682104</v>
       </c>
       <c r="N78" s="0">
         <v>0</v>
@@ -3556,40 +3556,40 @@
         <v>9203</v>
       </c>
       <c r="B79" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C79" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D79" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E79" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F79" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G79" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H79" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I79" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J79" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K79" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L79" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M79" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N79" s="0">
         <v>0</v>
@@ -3600,40 +3600,40 @@
         <v>9350</v>
       </c>
       <c r="B80" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C80" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D80" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E80" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F80" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G80" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H80" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I80" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J80" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K80" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L80" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M80" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N80" s="0">
         <v>0</v>
@@ -3644,40 +3644,40 @@
         <v>9477</v>
       </c>
       <c r="B81" s="0">
-        <v>3.0634205647939703e-08</v>
+        <v>1.67053322690279e-07</v>
       </c>
       <c r="C81" s="0">
-        <v>0.25014550133858598</v>
+        <v>0.74996327531205997</v>
       </c>
       <c r="D81" s="0">
-        <v>18.6230209543351</v>
+        <v>17.104507303082102</v>
       </c>
       <c r="E81" s="0">
-        <v>-24.965</v>
+        <v>7.1346819787909004e-08</v>
       </c>
       <c r="F81" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.74999514187309202</v>
       </c>
       <c r="G81" s="0">
-        <v>37.108333333333299</v>
+        <v>18.688602894952901</v>
       </c>
       <c r="H81" s="0">
-        <v>-0.21275301638899</v>
+        <v>1.33386398955855e-08</v>
       </c>
       <c r="I81" s="0">
-        <v>-256.34614975713401</v>
+        <v>0.74841924226319401</v>
       </c>
       <c r="J81" s="0">
-        <v>145.13176548878499</v>
+        <v>20.022387122199099</v>
       </c>
       <c r="K81" s="0">
-        <v>-0.25014547070438031</v>
+        <v>-0.74996310825873724</v>
       </c>
       <c r="L81" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.74999507052627223</v>
       </c>
       <c r="M81" s="0">
-        <v>256.13339674074501</v>
+        <v>-0.74841922892455415</v>
       </c>
       <c r="N81" s="0">
         <v>1</v>
@@ -3688,40 +3688,40 @@
         <v>9585</v>
       </c>
       <c r="B82" s="0">
-        <v>1.38540965067006e-08</v>
+        <v>1.41041775987358e-08</v>
       </c>
       <c r="C82" s="0">
-        <v>0.24952146274504999</v>
+        <v>0.75019958536842002</v>
       </c>
       <c r="D82" s="0">
-        <v>18.8717531752757</v>
+        <v>18.901612655461399</v>
       </c>
       <c r="E82" s="0">
-        <v>-24.965</v>
+        <v>4.2549619120819001e-08</v>
       </c>
       <c r="F82" s="0">
-        <v>-15.4933333333333</v>
+        <v>0.97638362899493603</v>
       </c>
       <c r="G82" s="0">
-        <v>37.108333333333299</v>
+        <v>18.803541286344799</v>
       </c>
       <c r="H82" s="0">
-        <v>-0.24890247837256599</v>
+        <v>7.87830966295989e-09</v>
       </c>
       <c r="I82" s="0">
-        <v>-266.07805787153802</v>
+        <v>0.75004706309348401</v>
       </c>
       <c r="J82" s="0">
-        <v>150.67226445295299</v>
+        <v>20.3062183466233</v>
       </c>
       <c r="K82" s="0">
-        <v>-0.24952144889095348</v>
+        <v>-0.75019957126424242</v>
       </c>
       <c r="L82" s="0">
-        <v>-9.4716666666666995</v>
+        <v>-0.97638358644531686</v>
       </c>
       <c r="M82" s="0">
-        <v>265.82915539316548</v>
+        <v>-0.75004705521517434</v>
       </c>
       <c r="N82" s="0">
         <v>1</v>
@@ -3732,40 +3732,40 @@
         <v>9593</v>
       </c>
       <c r="B83" s="0">
-        <v>7.3168852761458003e-09</v>
+        <v>7.31688419373936e-09</v>
       </c>
       <c r="C83" s="0">
-        <v>0.24853314435763399</v>
+        <v>0.69959804519805102</v>
       </c>
       <c r="D83" s="0">
-        <v>1.5700161791673299</v>
+        <v>1.5700160793495701</v>
       </c>
       <c r="E83" s="0">
-        <v>-35.6470244857571</v>
+        <v>5.2983012828679097e-07</v>
       </c>
       <c r="F83" s="0">
-        <v>20.949980456985902</v>
+        <v>0.57257427264872596</v>
       </c>
       <c r="G83" s="0">
-        <v>0.96107756322725302</v>
+        <v>1.5700183633287801</v>
       </c>
       <c r="H83" s="0">
-        <v>-0.24999999962132199</v>
+        <v>3.6652468480504899e-07</v>
       </c>
       <c r="I83" s="0">
-        <v>-1.2993688863498001</v>
+        <v>0.61084978455068495</v>
       </c>
       <c r="J83" s="0">
-        <v>1.3172509011337401</v>
+        <v>1.57001719991897</v>
       </c>
       <c r="K83" s="0">
-        <v>-0.24853313704074873</v>
+        <v>-0.69959803788116681</v>
       </c>
       <c r="L83" s="0">
-        <v>-56.597004942742998</v>
+        <v>-0.57257374281859763</v>
       </c>
       <c r="M83" s="0">
-        <v>1.0493688867284781</v>
+        <v>-0.61084941802600012</v>
       </c>
       <c r="N83" s="0">
         <v>1</v>
@@ -3776,40 +3776,40 @@
         <v>9620</v>
       </c>
       <c r="B84" s="0">
-        <v>9.2487830551900599e-07</v>
+        <v>9.2505284807292707e-09</v>
       </c>
       <c r="C84" s="0">
-        <v>0.25323640981177298</v>
+        <v>0.74000943191457502</v>
       </c>
       <c r="D84" s="0">
-        <v>2.1470511890785202</v>
+        <v>2.14704664093769</v>
       </c>
       <c r="E84" s="0">
-        <v>-0.31925920750638398</v>
+        <v>1.15749774282915e-07</v>
       </c>
       <c r="F84" s="0">
-        <v>-0.73130614840855701</v>
+        <v>0.73812908328460103</v>
       </c>
       <c r="G84" s="0">
-        <v>1.8064802357844501</v>
+        <v>2.1470459634536501</v>
       </c>
       <c r="H84" s="0">
-        <v>-0.0248183885224595</v>
+        <v>8.0971019946432006e-08</v>
       </c>
       <c r="I84" s="0">
-        <v>-2.0190323774943399</v>
+        <v>0.72643678593100303</v>
       </c>
       <c r="J84" s="0">
-        <v>2.0463631747986599</v>
+        <v>2.1470459330610199</v>
       </c>
       <c r="K84" s="0">
-        <v>-0.25323548493346748</v>
+        <v>-0.74000942266404657</v>
       </c>
       <c r="L84" s="0">
-        <v>0.41204694090217303</v>
+        <v>-0.73812896753482671</v>
       </c>
       <c r="M84" s="0">
-        <v>1.9942139889718804</v>
+        <v>-0.72643670495998303</v>
       </c>
       <c r="N84" s="0">
         <v>1</v>
@@ -3820,40 +3820,40 @@
         <v>9779</v>
       </c>
       <c r="B85" s="0">
-        <v>0.044189793107494303</v>
+        <v>0.044189798171648802</v>
       </c>
       <c r="C85" s="0">
-        <v>0.25004536522222198</v>
+        <v>0.75142137302591505</v>
       </c>
       <c r="D85" s="0">
-        <v>1.0108910004065399</v>
+        <v>1.0108909903136101</v>
       </c>
       <c r="E85" s="0">
-        <v>0.0132840388140174</v>
+        <v>0.0132816886795267</v>
       </c>
       <c r="F85" s="0">
-        <v>-0.78353066500979895</v>
+        <v>0.75610836474561804</v>
       </c>
       <c r="G85" s="0">
-        <v>0.898466347582487</v>
+        <v>0.89847627919784301</v>
       </c>
       <c r="H85" s="0">
-        <v>0.13304204596365299</v>
+        <v>0.13304415181500401</v>
       </c>
       <c r="I85" s="0">
-        <v>-0.81718174631026297</v>
+        <v>0.74224280770288498</v>
       </c>
       <c r="J85" s="0">
-        <v>1.18421398653238</v>
+        <v>1.1841868248051</v>
       </c>
       <c r="K85" s="0">
-        <v>-0.20585557211472769</v>
+        <v>-0.70723157485426624</v>
       </c>
       <c r="L85" s="0">
-        <v>0.79681470382381636</v>
+        <v>-0.74282667606609132</v>
       </c>
       <c r="M85" s="0">
-        <v>0.95022379227391596</v>
+        <v>-0.60919865588788102</v>
       </c>
       <c r="N85" s="0">
         <v>0</v>
